--- a/data/BlocselonAN.xlsx
+++ b/data/BlocselonAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/youssef/Desktop/ricardo_gph_analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9461853-7F6F-3343-A0B1-4E77FB4E8276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8B0F7F-E6E4-6C44-A590-9726BCCB5AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" xr2:uid="{CFCBB697-5549-F947-ABBB-1DDAA11F5FB5}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{CFCBB697-5549-F947-ABBB-1DDAA11F5FB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -10873,13 +10873,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11218,6 +11217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1F9B7D-6BBF-234F-A8E6-6117CCB385B8}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S719"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -11295,7 +11295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2</v>
       </c>
@@ -11348,7 +11348,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -11401,7 +11401,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -11460,7 +11460,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5</v>
       </c>
@@ -11513,7 +11513,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>6</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>7</v>
       </c>
@@ -11622,7 +11622,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>10</v>
       </c>
@@ -11675,7 +11675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>11</v>
       </c>
@@ -11728,7 +11728,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>20</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>21</v>
       </c>
@@ -11834,7 +11834,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>30</v>
       </c>
@@ -11887,7 +11887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>31</v>
       </c>
@@ -11940,7 +11940,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>40</v>
       </c>
@@ -11993,7 +11993,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>41</v>
       </c>
@@ -12046,7 +12046,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>42</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>51</v>
       </c>
@@ -12152,7 +12152,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>52</v>
       </c>
@@ -12205,7 +12205,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>53</v>
       </c>
@@ -12258,7 +12258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>54</v>
       </c>
@@ -12311,7 +12311,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>55</v>
       </c>
@@ -12364,7 +12364,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>56</v>
       </c>
@@ -12417,7 +12417,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>57</v>
       </c>
@@ -12470,7 +12470,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>58</v>
       </c>
@@ -12523,7 +12523,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>59</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>60</v>
       </c>
@@ -12608,7 +12608,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>65</v>
       </c>
@@ -12661,7 +12661,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>66</v>
       </c>
@@ -12714,7 +12714,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>68</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>70</v>
       </c>
@@ -12820,7 +12820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>80</v>
       </c>
@@ -12873,7 +12873,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>89</v>
       </c>
@@ -12926,7 +12926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>90</v>
       </c>
@@ -12979,7 +12979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>91</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>92</v>
       </c>
@@ -13085,7 +13085,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>93</v>
       </c>
@@ -13138,7 +13138,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>94</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>95</v>
       </c>
@@ -13244,7 +13244,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>96</v>
       </c>
@@ -13297,7 +13297,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>100</v>
       </c>
@@ -13350,7 +13350,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>101</v>
       </c>
@@ -13403,7 +13403,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>110</v>
       </c>
@@ -13456,7 +13456,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>115</v>
       </c>
@@ -13509,7 +13509,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>120</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>130</v>
       </c>
@@ -13615,7 +13615,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>135</v>
       </c>
@@ -13668,7 +13668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>136</v>
       </c>
@@ -13721,7 +13721,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>140</v>
       </c>
@@ -13774,7 +13774,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>145</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>150</v>
       </c>
@@ -13880,7 +13880,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>155</v>
       </c>
@@ -13933,7 +13933,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>160</v>
       </c>
@@ -13986,7 +13986,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>165</v>
       </c>
@@ -14039,7 +14039,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>200</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>205</v>
       </c>
@@ -14151,7 +14151,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>210</v>
       </c>
@@ -14204,7 +14204,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>211</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>212</v>
       </c>
@@ -14310,7 +14310,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>220</v>
       </c>
@@ -14363,7 +14363,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>221</v>
       </c>
@@ -14416,7 +14416,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>223</v>
       </c>
@@ -14469,7 +14469,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>225</v>
       </c>
@@ -14522,7 +14522,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>230</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>231</v>
       </c>
@@ -14628,7 +14628,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>232</v>
       </c>
@@ -14681,7 +14681,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>235</v>
       </c>
@@ -14734,7 +14734,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>239</v>
       </c>
@@ -14787,7 +14787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>240</v>
       </c>
@@ -14840,7 +14840,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>241</v>
       </c>
@@ -14893,7 +14893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>242</v>
       </c>
@@ -14946,7 +14946,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>243</v>
       </c>
@@ -14999,7 +14999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>244</v>
       </c>
@@ -15052,7 +15052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>245</v>
       </c>
@@ -15105,7 +15105,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>246</v>
       </c>
@@ -15158,7 +15158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>247</v>
       </c>
@@ -15211,7 +15211,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>248</v>
       </c>
@@ -15264,7 +15264,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>250</v>
       </c>
@@ -15317,7 +15317,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>251</v>
       </c>
@@ -15370,7 +15370,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>252</v>
       </c>
@@ -15423,7 +15423,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>253</v>
       </c>
@@ -15476,7 +15476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>254</v>
       </c>
@@ -15529,7 +15529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>255</v>
       </c>
@@ -15582,7 +15582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>256</v>
       </c>
@@ -15635,7 +15635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>257</v>
       </c>
@@ -15688,7 +15688,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>258</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>259</v>
       </c>
@@ -15794,7 +15794,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>261</v>
       </c>
@@ -15847,7 +15847,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>262</v>
       </c>
@@ -15900,7 +15900,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>264</v>
       </c>
@@ -15953,7 +15953,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>265</v>
       </c>
@@ -15979,7 +15979,7 @@
         <v>3557</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>266</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>267</v>
       </c>
@@ -16085,7 +16085,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>268</v>
       </c>
@@ -16138,7 +16138,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>269</v>
       </c>
@@ -16191,7 +16191,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>270</v>
       </c>
@@ -16244,7 +16244,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>271</v>
       </c>
@@ -16297,7 +16297,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>272</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>273</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>274</v>
       </c>
@@ -16456,7 +16456,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>275</v>
       </c>
@@ -16509,7 +16509,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>276</v>
       </c>
@@ -16562,7 +16562,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>277</v>
       </c>
@@ -16615,7 +16615,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>280</v>
       </c>
@@ -16668,7 +16668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>290</v>
       </c>
@@ -16724,7 +16724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>291</v>
       </c>
@@ -16780,7 +16780,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>300</v>
       </c>
@@ -16833,7 +16833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>305</v>
       </c>
@@ -16886,7 +16886,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>310</v>
       </c>
@@ -16942,7 +16942,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>315</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>316</v>
       </c>
@@ -17024,7 +17024,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>317</v>
       </c>
@@ -17050,7 +17050,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>324</v>
       </c>
@@ -17103,7 +17103,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>325</v>
       </c>
@@ -17156,7 +17156,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>327</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>328</v>
       </c>
@@ -17262,7 +17262,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>329</v>
       </c>
@@ -17315,7 +17315,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>331</v>
       </c>
@@ -17368,7 +17368,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>332</v>
       </c>
@@ -17421,7 +17421,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>335</v>
       </c>
@@ -17474,7 +17474,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>337</v>
       </c>
@@ -17527,7 +17527,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>338</v>
       </c>
@@ -17580,7 +17580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>339</v>
       </c>
@@ -17636,7 +17636,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>341</v>
       </c>
@@ -17689,7 +17689,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>342</v>
       </c>
@@ -17742,7 +17742,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>343</v>
       </c>
@@ -17771,7 +17771,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>344</v>
       </c>
@@ -17812,7 +17812,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>345</v>
       </c>
@@ -17865,7 +17865,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>346</v>
       </c>
@@ -17918,7 +17918,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>347</v>
       </c>
@@ -17947,7 +17947,7 @@
         <v>3561</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>348</v>
       </c>
@@ -17964,7 +17964,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>349</v>
       </c>
@@ -17987,7 +17987,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>350</v>
       </c>
@@ -18040,7 +18040,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>351</v>
       </c>
@@ -18093,7 +18093,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>352</v>
       </c>
@@ -18146,7 +18146,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>355</v>
       </c>
@@ -18202,7 +18202,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>359</v>
       </c>
@@ -18231,7 +18231,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>360</v>
       </c>
@@ -18287,7 +18287,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>365</v>
       </c>
@@ -18343,7 +18343,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>366</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>367</v>
       </c>
@@ -18455,7 +18455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>368</v>
       </c>
@@ -18511,7 +18511,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>369</v>
       </c>
@@ -18567,7 +18567,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>370</v>
       </c>
@@ -18596,7 +18596,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>371</v>
       </c>
@@ -18652,7 +18652,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>372</v>
       </c>
@@ -18708,7 +18708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>373</v>
       </c>
@@ -18734,7 +18734,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>375</v>
       </c>
@@ -18787,7 +18787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>380</v>
       </c>
@@ -18840,7 +18840,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>385</v>
       </c>
@@ -18893,7 +18893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>390</v>
       </c>
@@ -18946,7 +18946,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>395</v>
       </c>
@@ -18999,7 +18999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>401</v>
       </c>
@@ -19052,7 +19052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>402</v>
       </c>
@@ -19105,7 +19105,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>403</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>404</v>
       </c>
@@ -19211,7 +19211,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>411</v>
       </c>
@@ -19264,7 +19264,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>413</v>
       </c>
@@ -19317,7 +19317,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>420</v>
       </c>
@@ -19370,7 +19370,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>430</v>
       </c>
@@ -19423,7 +19423,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>432</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>433</v>
       </c>
@@ -19529,7 +19529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>434</v>
       </c>
@@ -19582,7 +19582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>435</v>
       </c>
@@ -19592,7 +19592,7 @@
       <c r="C163" t="s">
         <v>687</v>
       </c>
-      <c r="F163" s="5" t="s">
+      <c r="F163" t="s">
         <v>695</v>
       </c>
       <c r="I163" t="s">
@@ -19611,7 +19611,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>436</v>
       </c>
@@ -19664,7 +19664,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>437</v>
       </c>
@@ -19717,7 +19717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>438</v>
       </c>
@@ -19770,7 +19770,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>439</v>
       </c>
@@ -19780,7 +19780,7 @@
       <c r="C167" t="s">
         <v>687</v>
       </c>
-      <c r="F167" s="5" t="s">
+      <c r="F167" t="s">
         <v>695</v>
       </c>
       <c r="I167" t="s">
@@ -19814,7 +19814,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>450</v>
       </c>
@@ -19867,7 +19867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>451</v>
       </c>
@@ -19920,7 +19920,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>452</v>
       </c>
@@ -19973,7 +19973,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>460</v>
       </c>
@@ -20026,7 +20026,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>461</v>
       </c>
@@ -20079,7 +20079,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>462</v>
       </c>
@@ -20132,7 +20132,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>470</v>
       </c>
@@ -20185,7 +20185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>471</v>
       </c>
@@ -20238,7 +20238,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>472</v>
       </c>
@@ -20291,7 +20291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>475</v>
       </c>
@@ -20344,7 +20344,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>480</v>
       </c>
@@ -20397,7 +20397,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>481</v>
       </c>
@@ -20450,7 +20450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>482</v>
       </c>
@@ -20460,7 +20460,7 @@
       <c r="C180" t="s">
         <v>687</v>
       </c>
-      <c r="F180" s="5" t="s">
+      <c r="F180" t="s">
         <v>695</v>
       </c>
       <c r="I180" t="s">
@@ -20482,7 +20482,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>483</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>484</v>
       </c>
@@ -20588,7 +20588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>490</v>
       </c>
@@ -20641,7 +20641,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>500</v>
       </c>
@@ -20694,7 +20694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>501</v>
       </c>
@@ -20747,7 +20747,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>510</v>
       </c>
@@ -20800,7 +20800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>511</v>
       </c>
@@ -20853,7 +20853,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>512</v>
       </c>
@@ -20906,7 +20906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>515</v>
       </c>
@@ -20959,7 +20959,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>516</v>
       </c>
@@ -21012,7 +21012,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>517</v>
       </c>
@@ -21065,7 +21065,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>520</v>
       </c>
@@ -21118,7 +21118,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>521</v>
       </c>
@@ -21171,7 +21171,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>522</v>
       </c>
@@ -21224,7 +21224,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>530</v>
       </c>
@@ -21277,7 +21277,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>531</v>
       </c>
@@ -21330,7 +21330,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>540</v>
       </c>
@@ -21383,7 +21383,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>541</v>
       </c>
@@ -21436,7 +21436,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>551</v>
       </c>
@@ -21489,7 +21489,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>552</v>
       </c>
@@ -21542,7 +21542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>553</v>
       </c>
@@ -21595,7 +21595,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>560</v>
       </c>
@@ -21648,7 +21648,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>561</v>
       </c>
@@ -21701,7 +21701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>562</v>
       </c>
@@ -21754,7 +21754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>563</v>
       </c>
@@ -21807,7 +21807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>564</v>
       </c>
@@ -21860,7 +21860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>565</v>
       </c>
@@ -21913,7 +21913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>570</v>
       </c>
@@ -21966,7 +21966,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>571</v>
       </c>
@@ -22019,7 +22019,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>572</v>
       </c>
@@ -22072,7 +22072,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>580</v>
       </c>
@@ -22125,7 +22125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>581</v>
       </c>
@@ -22178,7 +22178,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>585</v>
       </c>
@@ -22231,7 +22231,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>590</v>
       </c>
@@ -22284,7 +22284,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>591</v>
       </c>
@@ -22337,7 +22337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>600</v>
       </c>
@@ -22390,7 +22390,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>601</v>
       </c>
@@ -22443,7 +22443,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>602</v>
       </c>
@@ -22496,7 +22496,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>615</v>
       </c>
@@ -22549,7 +22549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>616</v>
       </c>
@@ -22602,7 +22602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>620</v>
       </c>
@@ -22655,7 +22655,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>625</v>
       </c>
@@ -22708,7 +22708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>626</v>
       </c>
@@ -22718,14 +22718,14 @@
       <c r="C223" t="s">
         <v>687</v>
       </c>
-      <c r="F223" s="5" t="s">
+      <c r="F223" t="s">
         <v>695</v>
       </c>
       <c r="I223" t="s">
         <v>3503</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>630</v>
       </c>
@@ -22778,7 +22778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>640</v>
       </c>
@@ -22831,7 +22831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>645</v>
       </c>
@@ -22940,7 +22940,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>652</v>
       </c>
@@ -22996,7 +22996,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>660</v>
       </c>
@@ -23028,7 +23028,7 @@
         <v>3523</v>
       </c>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>663</v>
       </c>
@@ -23057,7 +23057,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>665</v>
       </c>
@@ -23113,7 +23113,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>666</v>
       </c>
@@ -23123,16 +23123,14 @@
       <c r="C232" t="s">
         <v>1061</v>
       </c>
-      <c r="F232" s="5" t="s">
+      <c r="F232" t="s">
         <v>1062</v>
       </c>
-      <c r="G232" s="5"/>
-      <c r="H232" s="5"/>
       <c r="I232" t="s">
         <v>1277</v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>670</v>
       </c>
@@ -23185,7 +23183,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>672</v>
       </c>
@@ -23238,7 +23236,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>674</v>
       </c>
@@ -23291,7 +23289,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>678</v>
       </c>
@@ -23347,7 +23345,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>679</v>
       </c>
@@ -23364,7 +23362,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>680</v>
       </c>
@@ -23384,7 +23382,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>681</v>
       </c>
@@ -23437,7 +23435,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>690</v>
       </c>
@@ -23490,7 +23488,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>692</v>
       </c>
@@ -23543,7 +23541,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>694</v>
       </c>
@@ -23596,7 +23594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>696</v>
       </c>
@@ -23649,7 +23647,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>698</v>
       </c>
@@ -23702,7 +23700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>700</v>
       </c>
@@ -23758,7 +23756,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>701</v>
       </c>
@@ -23784,7 +23782,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>702</v>
       </c>
@@ -23810,7 +23808,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>703</v>
       </c>
@@ -23833,7 +23831,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>704</v>
       </c>
@@ -23862,7 +23860,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>705</v>
       </c>
@@ -23885,7 +23883,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>710</v>
       </c>
@@ -23941,7 +23939,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>711</v>
       </c>
@@ -23997,7 +23995,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>712</v>
       </c>
@@ -24053,7 +24051,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>713</v>
       </c>
@@ -24109,7 +24107,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>720</v>
       </c>
@@ -24165,7 +24163,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>721</v>
       </c>
@@ -24221,7 +24219,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>730</v>
       </c>
@@ -24277,7 +24275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>731</v>
       </c>
@@ -24300,7 +24298,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>732</v>
       </c>
@@ -24323,7 +24321,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>735</v>
       </c>
@@ -24376,7 +24374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>740</v>
       </c>
@@ -24432,7 +24430,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>741</v>
       </c>
@@ -24488,7 +24486,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>750</v>
       </c>
@@ -24544,7 +24542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>751</v>
       </c>
@@ -24600,7 +24598,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>752</v>
       </c>
@@ -24656,7 +24654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>760</v>
       </c>
@@ -24712,7 +24710,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>761</v>
       </c>
@@ -24768,7 +24766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>770</v>
       </c>
@@ -24791,7 +24789,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>771</v>
       </c>
@@ -24814,7 +24812,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>775</v>
       </c>
@@ -24870,7 +24868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>780</v>
       </c>
@@ -24926,7 +24924,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>781</v>
       </c>
@@ -24982,7 +24980,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>790</v>
       </c>
@@ -25038,7 +25036,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>800</v>
       </c>
@@ -25094,7 +25092,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>810</v>
       </c>
@@ -25150,7 +25148,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>811</v>
       </c>
@@ -25206,7 +25204,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>812</v>
       </c>
@@ -25241,7 +25239,7 @@
         <v>3522</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>815</v>
       </c>
@@ -25297,7 +25295,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>820</v>
       </c>
@@ -25326,7 +25324,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>821</v>
       </c>
@@ -25382,7 +25380,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>823</v>
       </c>
@@ -25438,7 +25436,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>824</v>
       </c>
@@ -25494,7 +25492,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>827</v>
       </c>
@@ -25550,7 +25548,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>830</v>
       </c>
@@ -25585,7 +25583,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>835</v>
       </c>
@@ -25641,7 +25639,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>840</v>
       </c>
@@ -25697,7 +25695,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>850</v>
       </c>
@@ -25753,7 +25751,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>860</v>
       </c>
@@ -25809,7 +25807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>900</v>
       </c>
@@ -25865,7 +25863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>901</v>
       </c>
@@ -25921,7 +25919,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>902</v>
       </c>
@@ -25977,7 +25975,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>903</v>
       </c>
@@ -26033,7 +26031,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="293" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>904</v>
       </c>
@@ -26089,7 +26087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="294" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>905</v>
       </c>
@@ -26145,7 +26143,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="295" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>906</v>
       </c>
@@ -26201,7 +26199,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="296" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>910</v>
       </c>
@@ -26227,7 +26225,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="297" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>911</v>
       </c>
@@ -26283,7 +26281,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="298" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>912</v>
       </c>
@@ -26339,7 +26337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="299" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>920</v>
       </c>
@@ -26395,7 +26393,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="300" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>925</v>
       </c>
@@ -26451,7 +26449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="301" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>930</v>
       </c>
@@ -26507,7 +26505,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="302" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>935</v>
       </c>
@@ -26563,7 +26561,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="303" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>940</v>
       </c>
@@ -26619,7 +26617,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="304" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>945</v>
       </c>
@@ -26675,7 +26673,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="305" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>946</v>
       </c>
@@ -26704,7 +26702,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="306" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>947</v>
       </c>
@@ -26733,7 +26731,7 @@
         <v>3580</v>
       </c>
     </row>
-    <row r="307" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>950</v>
       </c>
@@ -26789,7 +26787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="308" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>955</v>
       </c>
@@ -26845,7 +26843,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="309" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>960</v>
       </c>
@@ -26901,7 +26899,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="310" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>970</v>
       </c>
@@ -26957,7 +26955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="311" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>980</v>
       </c>
@@ -27013,7 +27011,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="312" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>983</v>
       </c>
@@ -27069,7 +27067,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="313" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>985</v>
       </c>
@@ -27125,7 +27123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="314" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>986</v>
       </c>
@@ -27151,7 +27149,7 @@
         <v>3576</v>
       </c>
     </row>
-    <row r="315" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>987</v>
       </c>
@@ -27180,7 +27178,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="316" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>990</v>
       </c>
@@ -27236,7 +27234,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="317" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>991</v>
       </c>
@@ -27292,7 +27290,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="318" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>1001</v>
       </c>
@@ -27345,7 +27343,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="319" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>1002</v>
       </c>
@@ -27398,7 +27396,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="320" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>1016</v>
       </c>
@@ -27451,7 +27449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>1019</v>
       </c>
@@ -27507,7 +27505,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1020</v>
       </c>
@@ -27560,7 +27558,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>1022</v>
       </c>
@@ -27613,7 +27611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>1023</v>
       </c>
@@ -27666,7 +27664,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>1024</v>
       </c>
@@ -27719,7 +27717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>1025</v>
       </c>
@@ -27772,7 +27770,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>1026</v>
       </c>
@@ -27825,7 +27823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>1027</v>
       </c>
@@ -27878,7 +27876,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>1028</v>
       </c>
@@ -27931,7 +27929,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>1029</v>
       </c>
@@ -27984,7 +27982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>1032</v>
       </c>
@@ -28037,7 +28035,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>1033</v>
       </c>
@@ -28090,7 +28088,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>1044</v>
       </c>
@@ -28143,7 +28141,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>1048</v>
       </c>
@@ -28196,7 +28194,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>1049</v>
       </c>
@@ -28249,7 +28247,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>1053</v>
       </c>
@@ -28302,7 +28300,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>1054</v>
       </c>
@@ -28355,7 +28353,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>1055</v>
       </c>
@@ -28408,7 +28406,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>1058</v>
       </c>
@@ -28461,7 +28459,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="340" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>1061</v>
       </c>
@@ -28514,7 +28512,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>1062</v>
       </c>
@@ -28567,7 +28565,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>1063</v>
       </c>
@@ -28620,7 +28618,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>1064</v>
       </c>
@@ -28673,7 +28671,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="344" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>1065</v>
       </c>
@@ -28699,7 +28697,7 @@
         <v>3507</v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>1069</v>
       </c>
@@ -28722,7 +28720,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>1072</v>
       </c>
@@ -28775,7 +28773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>1073</v>
       </c>
@@ -28798,7 +28796,7 @@
         <v>3507</v>
       </c>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>1075</v>
       </c>
@@ -28851,7 +28849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>1076</v>
       </c>
@@ -28904,7 +28902,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>1081</v>
       </c>
@@ -28957,7 +28955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>1087</v>
       </c>
@@ -29013,7 +29011,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>1094</v>
       </c>
@@ -29066,7 +29064,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>1102</v>
       </c>
@@ -29122,7 +29120,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="354" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1103</v>
       </c>
@@ -29178,7 +29176,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>1105</v>
       </c>
@@ -29231,7 +29229,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>1106</v>
       </c>
@@ -29284,7 +29282,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>1111</v>
       </c>
@@ -29340,7 +29338,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>1156</v>
       </c>
@@ -29393,7 +29391,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>1161</v>
       </c>
@@ -29446,7 +29444,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>1163</v>
       </c>
@@ -29499,7 +29497,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>1164</v>
       </c>
@@ -29552,7 +29550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>2003</v>
       </c>
@@ -29608,7 +29606,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>2004</v>
       </c>
@@ -29664,7 +29662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>2101</v>
       </c>
@@ -29717,7 +29715,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>2111</v>
       </c>
@@ -29770,7 +29768,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>2246</v>
       </c>
@@ -29823,7 +29821,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>2247</v>
       </c>
@@ -29876,7 +29874,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>2248</v>
       </c>
@@ -29929,7 +29927,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>2249</v>
       </c>
@@ -29982,7 +29980,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>2311</v>
       </c>
@@ -30035,7 +30033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>2333</v>
       </c>
@@ -30088,7 +30086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>2556</v>
       </c>
@@ -30141,7 +30139,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>2901</v>
       </c>
@@ -30194,7 +30192,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>2902</v>
       </c>
@@ -30250,7 +30248,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>2903</v>
       </c>
@@ -30306,7 +30304,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>3271</v>
       </c>
@@ -30359,7 +30357,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>3327</v>
       </c>
@@ -30412,7 +30410,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>3340</v>
       </c>
@@ -30465,7 +30463,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>3343</v>
       </c>
@@ -30518,7 +30516,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>3349</v>
       </c>
@@ -30571,7 +30569,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>3353</v>
       </c>
@@ -30624,7 +30622,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>3361</v>
       </c>
@@ -30680,7 +30678,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>3362</v>
       </c>
@@ -30736,7 +30734,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>3363</v>
       </c>
@@ -30792,7 +30790,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>3386</v>
       </c>
@@ -30845,7 +30843,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>3471</v>
       </c>
@@ -30898,7 +30896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>3502</v>
       </c>
@@ -30951,7 +30949,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="388" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>3503</v>
       </c>
@@ -31004,7 +31002,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="389" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>3504</v>
       </c>
@@ -31057,7 +31055,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>3551</v>
       </c>
@@ -31113,7 +31111,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>3654</v>
       </c>
@@ -31166,7 +31164,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>3761</v>
       </c>
@@ -31219,7 +31217,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>3762</v>
       </c>
@@ -31272,7 +31270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>3805</v>
       </c>
@@ -31325,7 +31323,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="395" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>4041</v>
       </c>
@@ -31378,7 +31376,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>4042</v>
       </c>
@@ -31431,7 +31429,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>4044</v>
       </c>
@@ -31484,7 +31482,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>4050</v>
       </c>
@@ -31537,7 +31535,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>4060</v>
       </c>
@@ -31590,7 +31588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>4070</v>
       </c>
@@ -31643,7 +31641,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="401" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>4111</v>
       </c>
@@ -31696,7 +31694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="402" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>4112</v>
       </c>
@@ -31749,7 +31747,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="403" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>4325</v>
       </c>
@@ -31802,7 +31800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="404" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>4326</v>
       </c>
@@ -31855,7 +31853,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="405" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>4327</v>
       </c>
@@ -31908,7 +31906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="406" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>4328</v>
       </c>
@@ -31961,7 +31959,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="407" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>4331</v>
       </c>
@@ -32014,7 +32012,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="408" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>4332</v>
       </c>
@@ -32067,7 +32065,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="409" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>4333</v>
       </c>
@@ -32120,7 +32118,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="410" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>4334</v>
       </c>
@@ -32173,7 +32171,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="411" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>4335</v>
       </c>
@@ -32226,7 +32224,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="412" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>4336</v>
       </c>
@@ -32279,7 +32277,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="413" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>4337</v>
       </c>
@@ -32332,7 +32330,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="414" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>4338</v>
       </c>
@@ -32385,7 +32383,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="415" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>4341</v>
       </c>
@@ -32438,7 +32436,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="416" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>4343</v>
       </c>
@@ -32491,7 +32489,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="417" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>4345</v>
       </c>
@@ -32544,7 +32542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="418" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>4347</v>
       </c>
@@ -32597,7 +32595,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="419" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>4348</v>
       </c>
@@ -32650,7 +32648,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="420" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>4349</v>
       </c>
@@ -32703,7 +32701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="421" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>4352</v>
       </c>
@@ -32756,7 +32754,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="422" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>4354</v>
       </c>
@@ -32809,7 +32807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="423" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>4361</v>
       </c>
@@ -32862,7 +32860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="424" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>4362</v>
       </c>
@@ -32915,7 +32913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="425" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>4381</v>
       </c>
@@ -32968,7 +32966,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="426" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>4382</v>
       </c>
@@ -33021,7 +33019,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="427" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>4383</v>
       </c>
@@ -33074,7 +33072,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="428" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>4391</v>
       </c>
@@ -33127,7 +33125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="429" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>4392</v>
       </c>
@@ -33180,7 +33178,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="430" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>4394</v>
       </c>
@@ -33233,7 +33231,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="431" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>4395</v>
       </c>
@@ -33286,7 +33284,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="432" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>4396</v>
       </c>
@@ -33339,7 +33337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="433" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>4397</v>
       </c>
@@ -33392,7 +33390,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="434" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>4501</v>
       </c>
@@ -33445,7 +33443,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="435" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>4515</v>
       </c>
@@ -33498,7 +33496,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="436" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>4521</v>
       </c>
@@ -33551,7 +33549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="437" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>4527</v>
       </c>
@@ -33604,7 +33602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="438" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>4529</v>
       </c>
@@ -33657,7 +33655,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="439" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>4534</v>
       </c>
@@ -33710,7 +33708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="440" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>4535</v>
       </c>
@@ -33763,7 +33761,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="441" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>4711</v>
       </c>
@@ -33816,7 +33814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="442" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>4737</v>
       </c>
@@ -33869,7 +33867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="443" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>4741</v>
       </c>
@@ -33922,7 +33920,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="444" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>4742</v>
       </c>
@@ -33975,7 +33973,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="445" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>4744</v>
       </c>
@@ -34028,7 +34026,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="446" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>4746</v>
       </c>
@@ -34081,7 +34079,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="447" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>4751</v>
       </c>
@@ -34134,7 +34132,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="448" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>4763</v>
       </c>
@@ -34187,7 +34185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="449" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>4769</v>
       </c>
@@ -34240,7 +34238,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="450" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>4773</v>
       </c>
@@ -34293,7 +34291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="451" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>4776</v>
       </c>
@@ -34346,7 +34344,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="452" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>4781</v>
       </c>
@@ -34399,7 +34397,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="453" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>4782</v>
       </c>
@@ -34452,7 +34450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="454" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>4783</v>
       </c>
@@ -34505,7 +34503,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="455" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>4784</v>
       </c>
@@ -34558,7 +34556,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="456" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>4791</v>
       </c>
@@ -34611,7 +34609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="457" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>4792</v>
       </c>
@@ -34664,7 +34662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="458" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>4793</v>
       </c>
@@ -34717,7 +34715,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="459" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>4795</v>
       </c>
@@ -34770,7 +34768,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="460" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>4821</v>
       </c>
@@ -34823,7 +34821,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="461" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>4822</v>
       </c>
@@ -34876,7 +34874,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="462" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>4831</v>
       </c>
@@ -34929,7 +34927,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="463" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>4832</v>
       </c>
@@ -34982,7 +34980,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="464" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>4841</v>
       </c>
@@ -35035,7 +35033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="465" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>4842</v>
       </c>
@@ -35088,7 +35086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="466" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>4902</v>
       </c>
@@ -35141,7 +35139,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>4904</v>
       </c>
@@ -35194,7 +35192,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="468" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>4908</v>
       </c>
@@ -35247,7 +35245,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="469" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469">
         <v>4910</v>
       </c>
@@ -35300,7 +35298,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="470" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>5001</v>
       </c>
@@ -35353,7 +35351,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="471" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>5002</v>
       </c>
@@ -35406,7 +35404,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="472" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>5003</v>
       </c>
@@ -35459,7 +35457,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="473" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>5011</v>
       </c>
@@ -35512,7 +35510,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="474" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474">
         <v>5013</v>
       </c>
@@ -35565,7 +35563,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="475" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>5018</v>
       </c>
@@ -35618,7 +35616,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="476" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>5102</v>
       </c>
@@ -35671,7 +35669,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="477" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>5104</v>
       </c>
@@ -35724,7 +35722,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="478" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>5109</v>
       </c>
@@ -35780,7 +35778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="479" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479">
         <v>5200</v>
       </c>
@@ -35833,7 +35831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="480" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>5201</v>
       </c>
@@ -35886,7 +35884,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="481" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>5203</v>
       </c>
@@ -35939,7 +35937,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="482" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>5212</v>
       </c>
@@ -35992,7 +35990,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="483" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>5303</v>
       </c>
@@ -36045,7 +36043,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="484" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>5306</v>
       </c>
@@ -36098,7 +36096,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="485" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>5307</v>
       </c>
@@ -36151,7 +36149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="486" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>5309</v>
       </c>
@@ -36204,7 +36202,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="487" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>5321</v>
       </c>
@@ -36257,7 +36255,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="488" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>5322</v>
       </c>
@@ -36310,7 +36308,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="489" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>5323</v>
       </c>
@@ -36363,7 +36361,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="490" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>5324</v>
       </c>
@@ -36416,7 +36414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="491" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>5332</v>
       </c>
@@ -36469,7 +36467,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="492" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>5403</v>
       </c>
@@ -36522,7 +36520,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="493" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>5511</v>
       </c>
@@ -36575,7 +36573,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="494" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>5512</v>
       </c>
@@ -36628,7 +36626,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="495" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>5513</v>
       </c>
@@ -36681,7 +36679,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="496" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>5516</v>
       </c>
@@ -36734,7 +36732,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="497" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>5517</v>
       </c>
@@ -36787,7 +36785,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="498" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>5518</v>
       </c>
@@ -36840,7 +36838,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="499" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>5519</v>
       </c>
@@ -36893,7 +36891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="500" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>5522</v>
       </c>
@@ -36946,7 +36944,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="501" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>5523</v>
       </c>
@@ -36999,7 +36997,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="502" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>5606</v>
       </c>
@@ -37052,7 +37050,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="503" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>5611</v>
       </c>
@@ -37105,7 +37103,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="504" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>5614</v>
       </c>
@@ -37158,7 +37156,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="505" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>5621</v>
       </c>
@@ -37211,7 +37209,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="506" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>5641</v>
       </c>
@@ -37264,7 +37262,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="507" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507">
         <v>5642</v>
       </c>
@@ -37317,7 +37315,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="508" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508">
         <v>5651</v>
       </c>
@@ -37370,7 +37368,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="509" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>5796</v>
       </c>
@@ -37423,7 +37421,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="510" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>5799</v>
       </c>
@@ -37476,7 +37474,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="511" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>5801</v>
       </c>
@@ -37529,7 +37527,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="512" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512">
         <v>5802</v>
       </c>
@@ -37582,7 +37580,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="513" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>5803</v>
       </c>
@@ -37635,7 +37633,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="514" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>5811</v>
       </c>
@@ -37688,7 +37686,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="515" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>5812</v>
       </c>
@@ -37741,7 +37739,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="516" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516">
         <v>5813</v>
       </c>
@@ -37794,7 +37792,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="517" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517">
         <v>5814</v>
       </c>
@@ -37847,7 +37845,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="518" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518">
         <v>5901</v>
       </c>
@@ -37900,7 +37898,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="519" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519">
         <v>5902</v>
       </c>
@@ -37953,7 +37951,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="520" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520">
         <v>5903</v>
       </c>
@@ -38006,7 +38004,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="521" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521">
         <v>6030</v>
       </c>
@@ -38059,7 +38057,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="522" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522">
         <v>6062</v>
       </c>
@@ -38115,7 +38113,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="523" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523">
         <v>6064</v>
       </c>
@@ -38171,7 +38169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="524" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524">
         <v>6067</v>
       </c>
@@ -38224,7 +38222,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="525" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525">
         <v>6090</v>
       </c>
@@ -38277,7 +38275,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="526" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526">
         <v>6151</v>
       </c>
@@ -38330,7 +38328,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="527" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527">
         <v>6202</v>
       </c>
@@ -38386,7 +38384,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="528" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528">
         <v>6203</v>
       </c>
@@ -38442,7 +38440,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="529" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529">
         <v>6251</v>
       </c>
@@ -38495,7 +38493,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="530" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530">
         <v>6255</v>
       </c>
@@ -38551,7 +38549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="531" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531">
         <v>6306</v>
       </c>
@@ -38604,7 +38602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="532" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532">
         <v>6401</v>
       </c>
@@ -38657,7 +38655,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="533" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533">
         <v>6402</v>
       </c>
@@ -38710,7 +38708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="534" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534">
         <v>6631</v>
       </c>
@@ -38736,7 +38734,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="535" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535">
         <v>6800</v>
       </c>
@@ -38789,7 +38787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="536" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536">
         <v>6802</v>
       </c>
@@ -38842,7 +38840,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="537" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537">
         <v>6811</v>
       </c>
@@ -38895,7 +38893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="538" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538">
         <v>6821</v>
       </c>
@@ -38948,7 +38946,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="539" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539">
         <v>6822</v>
       </c>
@@ -39001,7 +38999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="540" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540">
         <v>6823</v>
       </c>
@@ -39054,7 +39052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="541" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541">
         <v>6825</v>
       </c>
@@ -39107,7 +39105,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="542" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542">
         <v>6826</v>
       </c>
@@ -39160,7 +39158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="543" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543">
         <v>6828</v>
       </c>
@@ -39213,7 +39211,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="544" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544">
         <v>6832</v>
       </c>
@@ -39266,7 +39264,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="545" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545">
         <v>6833</v>
       </c>
@@ -39319,7 +39317,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="546" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546">
         <v>6844</v>
       </c>
@@ -39372,7 +39370,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="547" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547">
         <v>6845</v>
       </c>
@@ -39425,7 +39423,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="548" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548">
         <v>6846</v>
       </c>
@@ -39478,7 +39476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="549" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549">
         <v>6982</v>
       </c>
@@ -39531,7 +39529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="550" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550">
         <v>7010</v>
       </c>
@@ -39584,7 +39582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="551" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551">
         <v>7020</v>
       </c>
@@ -39637,7 +39635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="552" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552">
         <v>7030</v>
       </c>
@@ -39690,7 +39688,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="553" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553">
         <v>7104</v>
       </c>
@@ -39746,7 +39744,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="554" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554">
         <v>7105</v>
       </c>
@@ -39802,7 +39800,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="555" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555">
         <v>7106</v>
       </c>
@@ -39858,7 +39856,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="556" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556">
         <v>7110</v>
       </c>
@@ -39914,7 +39912,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="557" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557">
         <v>7111</v>
       </c>
@@ -39970,7 +39968,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="558" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558">
         <v>7120</v>
       </c>
@@ -40026,7 +40024,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="559" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559">
         <v>7121</v>
       </c>
@@ -40082,7 +40080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="560" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560">
         <v>7122</v>
       </c>
@@ -40138,7 +40136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="561" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561">
         <v>7124</v>
       </c>
@@ -40194,7 +40192,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="562" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562">
         <v>7125</v>
       </c>
@@ -40250,7 +40248,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="563" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563">
         <v>7127</v>
       </c>
@@ -40306,7 +40304,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="564" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564">
         <v>7136</v>
       </c>
@@ -40362,7 +40360,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="565" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565">
         <v>7137</v>
       </c>
@@ -40418,7 +40416,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="566" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566">
         <v>7351</v>
       </c>
@@ -40472,7 +40470,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="567" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567">
         <v>7352</v>
       </c>
@@ -40528,7 +40526,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="568" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568">
         <v>7411</v>
       </c>
@@ -40584,7 +40582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="569" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569">
         <v>7501</v>
       </c>
@@ -40640,7 +40638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="570" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570">
         <v>7502</v>
       </c>
@@ -40696,7 +40694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="571" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571">
         <v>7506</v>
       </c>
@@ -40752,7 +40750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="572" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572">
         <v>7508</v>
       </c>
@@ -40808,7 +40806,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="573" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573">
         <v>7511</v>
       </c>
@@ -40864,7 +40862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="574" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574">
         <v>7512</v>
       </c>
@@ -40920,7 +40918,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="575" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575">
         <v>7513</v>
       </c>
@@ -40976,7 +40974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="576" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576">
         <v>7514</v>
       </c>
@@ -41032,7 +41030,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="577" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577">
         <v>7515</v>
       </c>
@@ -41088,7 +41086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="578" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578">
         <v>7516</v>
       </c>
@@ -41144,7 +41142,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="579" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579">
         <v>7517</v>
       </c>
@@ -41200,7 +41198,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="580" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580">
         <v>7519</v>
       </c>
@@ -41256,7 +41254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="581" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581">
         <v>7521</v>
       </c>
@@ -41312,7 +41310,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="582" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582">
         <v>7522</v>
       </c>
@@ -41368,7 +41366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="583" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583">
         <v>7523</v>
       </c>
@@ -41424,7 +41422,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="584" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584">
         <v>7526</v>
       </c>
@@ -41480,7 +41478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="585" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585">
         <v>7527</v>
       </c>
@@ -41536,7 +41534,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="586" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586">
         <v>7528</v>
       </c>
@@ -41592,7 +41590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="587" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587">
         <v>7529</v>
       </c>
@@ -41648,7 +41646,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="588" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588">
         <v>7531</v>
       </c>
@@ -41704,7 +41702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="589" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589">
         <v>7532</v>
       </c>
@@ -41760,7 +41758,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="590" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590">
         <v>7533</v>
       </c>
@@ -41816,7 +41814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="591" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591">
         <v>7534</v>
       </c>
@@ -41872,7 +41870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="592" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592">
         <v>7535</v>
       </c>
@@ -41928,7 +41926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="593" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593">
         <v>7537</v>
       </c>
@@ -41984,7 +41982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="594" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594">
         <v>7538</v>
       </c>
@@ -42040,7 +42038,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="595" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595">
         <v>7539</v>
       </c>
@@ -42096,7 +42094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="596" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596">
         <v>7541</v>
       </c>
@@ -42152,7 +42150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="597" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597">
         <v>7542</v>
       </c>
@@ -42208,7 +42206,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="598" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598">
         <v>7543</v>
       </c>
@@ -42264,7 +42262,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="599" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599">
         <v>7544</v>
       </c>
@@ -42320,7 +42318,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="600" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600">
         <v>7545</v>
       </c>
@@ -42376,7 +42374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="601" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601">
         <v>7546</v>
       </c>
@@ -42432,7 +42430,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="602" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602">
         <v>7549</v>
       </c>
@@ -42488,7 +42486,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="603" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603">
         <v>7552</v>
       </c>
@@ -42544,7 +42542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="604" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604">
         <v>7553</v>
       </c>
@@ -42600,7 +42598,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="605" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605">
         <v>7570</v>
       </c>
@@ -42656,7 +42654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="606" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606">
         <v>7573</v>
       </c>
@@ -42712,7 +42710,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="607" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607">
         <v>7574</v>
       </c>
@@ -42768,7 +42766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="608" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608">
         <v>7577</v>
       </c>
@@ -42824,7 +42822,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="609" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609">
         <v>7579</v>
       </c>
@@ -42880,7 +42878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="610" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610">
         <v>7582</v>
       </c>
@@ -42936,7 +42934,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="611" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611">
         <v>7587</v>
       </c>
@@ -42992,7 +42990,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="612" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612">
         <v>7588</v>
       </c>
@@ -43048,7 +43046,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="613" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613">
         <v>7694</v>
       </c>
@@ -43104,7 +43102,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="614" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614">
         <v>7701</v>
       </c>
@@ -43160,7 +43158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="615" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615">
         <v>7702</v>
       </c>
@@ -43216,7 +43214,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="616" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616">
         <v>7703</v>
       </c>
@@ -43272,7 +43270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="617" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617">
         <v>7704</v>
       </c>
@@ -43328,7 +43326,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="618" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618">
         <v>7706</v>
       </c>
@@ -43384,7 +43382,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="619" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619">
         <v>7707</v>
       </c>
@@ -43443,7 +43441,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="620" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620">
         <v>7750</v>
       </c>
@@ -43499,7 +43497,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="621" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621">
         <v>7751</v>
       </c>
@@ -43555,7 +43553,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="622" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622">
         <v>7752</v>
       </c>
@@ -43611,7 +43609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="623" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623">
         <v>7755</v>
       </c>
@@ -43667,7 +43665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="624" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624">
         <v>7756</v>
       </c>
@@ -43723,7 +43721,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="625" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625">
         <v>7757</v>
       </c>
@@ -43779,7 +43777,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="626" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626">
         <v>7758</v>
       </c>
@@ -43835,7 +43833,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="627" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627">
         <v>7760</v>
       </c>
@@ -43891,7 +43889,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="628" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628">
         <v>7762</v>
       </c>
@@ -43947,7 +43945,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="629" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629">
         <v>7766</v>
       </c>
@@ -44003,7 +44001,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="630" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630">
         <v>7767</v>
       </c>
@@ -44059,7 +44057,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="631" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631">
         <v>7768</v>
       </c>
@@ -44115,7 +44113,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="632" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632">
         <v>7769</v>
       </c>
@@ -44171,7 +44169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="633" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633">
         <v>7770</v>
       </c>
@@ -44227,7 +44225,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="634" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634">
         <v>7771</v>
       </c>
@@ -44283,7 +44281,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="635" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635">
         <v>7772</v>
       </c>
@@ -44339,7 +44337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="636" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636">
         <v>7773</v>
       </c>
@@ -44395,7 +44393,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="637" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637">
         <v>7774</v>
       </c>
@@ -44451,7 +44449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="638" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638">
         <v>7775</v>
       </c>
@@ -44507,7 +44505,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="639" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639">
         <v>7776</v>
       </c>
@@ -44563,7 +44561,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="640" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640">
         <v>7777</v>
       </c>
@@ -44619,7 +44617,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="641" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641">
         <v>7778</v>
       </c>
@@ -44675,7 +44673,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="642" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642">
         <v>7779</v>
       </c>
@@ -44731,7 +44729,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="643" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643">
         <v>7780</v>
       </c>
@@ -44787,7 +44785,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="644" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644">
         <v>7782</v>
       </c>
@@ -44843,7 +44841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="645" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645">
         <v>7783</v>
       </c>
@@ -44899,7 +44897,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="646" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646">
         <v>7784</v>
       </c>
@@ -44955,7 +44953,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="647" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647">
         <v>7785</v>
       </c>
@@ -45011,7 +45009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="648" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648">
         <v>7786</v>
       </c>
@@ -45067,7 +45065,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="649" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649">
         <v>7787</v>
       </c>
@@ -45123,7 +45121,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="650" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650">
         <v>7788</v>
       </c>
@@ -45179,7 +45177,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="651" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651">
         <v>7789</v>
       </c>
@@ -45235,7 +45233,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="652" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652">
         <v>7790</v>
       </c>
@@ -45291,7 +45289,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="653" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653">
         <v>7791</v>
       </c>
@@ -45347,7 +45345,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="654" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654">
         <v>7792</v>
       </c>
@@ -45403,7 +45401,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="655" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655">
         <v>7793</v>
       </c>
@@ -45459,7 +45457,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="656" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656">
         <v>7794</v>
       </c>
@@ -45515,7 +45513,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="657" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657">
         <v>7795</v>
       </c>
@@ -45571,7 +45569,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="658" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658">
         <v>7796</v>
       </c>
@@ -45627,7 +45625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="659" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659">
         <v>7797</v>
       </c>
@@ -45683,7 +45681,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="660" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660">
         <v>8002</v>
       </c>
@@ -45739,7 +45737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="661" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661">
         <v>8124</v>
       </c>
@@ -45795,7 +45793,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="662" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662">
         <v>8151</v>
       </c>
@@ -45851,7 +45849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="663" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663">
         <v>8152</v>
       </c>
@@ -45907,7 +45905,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="664" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664">
         <v>8153</v>
       </c>
@@ -45963,7 +45961,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="665" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665">
         <v>8171</v>
       </c>
@@ -46019,7 +46017,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="666" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666">
         <v>8201</v>
       </c>
@@ -46075,7 +46073,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="667" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667">
         <v>8202</v>
       </c>
@@ -46131,7 +46129,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="668" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668">
         <v>8203</v>
       </c>
@@ -46187,7 +46185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="669" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669">
         <v>8210</v>
       </c>
@@ -46243,7 +46241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="670" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670">
         <v>8218</v>
       </c>
@@ -46299,7 +46297,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="671" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671">
         <v>8221</v>
       </c>
@@ -46355,7 +46353,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="672" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672">
         <v>8222</v>
       </c>
@@ -46411,7 +46409,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="673" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673">
         <v>8223</v>
       </c>
@@ -46467,7 +46465,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="674" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674">
         <v>8224</v>
       </c>
@@ -46523,7 +46521,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="675" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675">
         <v>8225</v>
       </c>
@@ -46579,7 +46577,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="676" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676">
         <v>8231</v>
       </c>
@@ -46635,7 +46633,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="677" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677">
         <v>8401</v>
       </c>
@@ -46691,7 +46689,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="678" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678">
         <v>8501</v>
       </c>
@@ -46747,7 +46745,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="679" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679">
         <v>8510</v>
       </c>
@@ -46803,7 +46801,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="680" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680">
         <v>8522</v>
       </c>
@@ -46859,7 +46857,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="681" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681">
         <v>8523</v>
       </c>
@@ -46915,7 +46913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="682" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682">
         <v>8531</v>
       </c>
@@ -46971,7 +46969,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="683" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683">
         <v>8532</v>
       </c>
@@ -47027,7 +47025,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="684" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684">
         <v>8533</v>
       </c>
@@ -47083,7 +47081,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="685" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685">
         <v>8536</v>
       </c>
@@ -47139,7 +47137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="686" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686">
         <v>8550</v>
       </c>
@@ -47195,7 +47193,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="687" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687">
         <v>8551</v>
       </c>
@@ -47251,7 +47249,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="688" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A688">
         <v>8560</v>
       </c>
@@ -47307,7 +47305,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="689" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689">
         <v>8571</v>
       </c>
@@ -47363,7 +47361,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="690" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690">
         <v>8572</v>
       </c>
@@ -47419,7 +47417,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="691" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691">
         <v>8574</v>
       </c>
@@ -47475,7 +47473,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="692" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692">
         <v>9002</v>
       </c>
@@ -47531,7 +47529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="693" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693">
         <v>9004</v>
       </c>
@@ -47590,7 +47588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="694" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694">
         <v>9006</v>
       </c>
@@ -47649,7 +47647,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="695" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695">
         <v>9008</v>
       </c>
@@ -47708,7 +47706,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="696" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696">
         <v>9050</v>
       </c>
@@ -47767,7 +47765,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="697" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697">
         <v>9201</v>
       </c>
@@ -47823,7 +47821,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="698" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698">
         <v>9205</v>
       </c>
@@ -47882,7 +47880,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="699" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699">
         <v>9252</v>
       </c>
@@ -47938,7 +47936,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="700" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700">
         <v>9253</v>
       </c>
@@ -47994,7 +47992,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="701" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701">
         <v>9321</v>
       </c>
@@ -48050,7 +48048,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="702" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702">
         <v>9453</v>
       </c>
@@ -48106,7 +48104,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="703" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703">
         <v>9462</v>
       </c>
@@ -48162,7 +48160,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="704" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704">
         <v>9601</v>
       </c>
@@ -48218,7 +48216,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="705" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705">
         <v>9602</v>
       </c>
@@ -48274,7 +48272,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="706" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706">
         <v>9603</v>
       </c>
@@ -48330,7 +48328,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="707" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A707">
         <v>9605</v>
       </c>
@@ -48386,7 +48384,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="708" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708">
         <v>9610</v>
       </c>
@@ -48442,7 +48440,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="709" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709">
         <v>9620</v>
       </c>
@@ -48498,7 +48496,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="710" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710">
         <v>9740</v>
       </c>
@@ -48557,7 +48555,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="711" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711">
         <v>9810</v>
       </c>
@@ -48616,7 +48614,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="712" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712">
         <v>9820</v>
       </c>
@@ -48672,7 +48670,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="713" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713">
         <v>9830</v>
       </c>
@@ -48728,7 +48726,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="714" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714">
         <v>9900</v>
       </c>
@@ -48784,7 +48782,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="715" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715">
         <v>9973</v>
       </c>
@@ -48840,7 +48838,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="716" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A716">
         <v>9974</v>
       </c>
@@ -48896,7 +48894,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="717" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717">
         <v>9994</v>
       </c>
@@ -48952,7 +48950,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="718" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718">
         <v>10200</v>
       </c>
@@ -49005,7 +49003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="719" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A719">
         <v>10210</v>
       </c>
@@ -49060,6 +49058,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:S719" xr:uid="{4F1F9B7D-6BBF-234F-A8E6-6117CCB385B8}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Egypt Arab Republic (Egypt)"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S719">
       <sortCondition ref="A1:A719"/>
     </sortState>

--- a/data/BlocselonAN.xlsx
+++ b/data/BlocselonAN.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/youssef/Desktop/ricardo_gph_analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8B0F7F-E6E4-6C44-A590-9726BCCB5AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C85018-DE99-034F-910C-98CA0F427A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{CFCBB697-5549-F947-ABBB-1DDAA11F5FB5}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{CFCBB697-5549-F947-ABBB-1DDAA11F5FB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$S$719</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$S$729</definedName>
     <definedName name="gph_with_AndersonNorheim_regions_and_periods" localSheetId="0">Feuil1!$A$1:$S$677</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11181" uniqueCount="3581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11216" uniqueCount="3591">
   <si>
     <t>GPH_code</t>
   </si>
@@ -10814,6 +10814,36 @@
   </si>
   <si>
     <t>2000-2022 | Sovereign | NA</t>
+  </si>
+  <si>
+    <t>Sindh</t>
+  </si>
+  <si>
+    <t>Republic of St. Mark</t>
+  </si>
+  <si>
+    <t>Heard and McDonald Is.</t>
+  </si>
+  <si>
+    <t>Grand Popo</t>
+  </si>
+  <si>
+    <t>Elobey, Annóbon and Corisco</t>
+  </si>
+  <si>
+    <t>Lord Howe I.</t>
+  </si>
+  <si>
+    <t>Tibet</t>
+  </si>
+  <si>
+    <t>Juan de Nova I.</t>
+  </si>
+  <si>
+    <t>Aden Protectorate</t>
+  </si>
+  <si>
+    <t>Northern Marianas Is.</t>
   </si>
 </sst>
 </file>
@@ -11217,8 +11247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F1F9B7D-6BBF-234F-A8E6-6117CCB385B8}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:S719"/>
+  <dimension ref="A1:S729"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -11295,7 +11324,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2</v>
       </c>
@@ -11348,7 +11377,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>3</v>
       </c>
@@ -11401,7 +11430,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
@@ -11460,7 +11489,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5</v>
       </c>
@@ -11513,7 +11542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>6</v>
       </c>
@@ -11566,7 +11595,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>7</v>
       </c>
@@ -11622,7 +11651,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>10</v>
       </c>
@@ -11675,7 +11704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>11</v>
       </c>
@@ -11728,7 +11757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>20</v>
       </c>
@@ -11781,7 +11810,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>21</v>
       </c>
@@ -11834,7 +11863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>30</v>
       </c>
@@ -11887,7 +11916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>31</v>
       </c>
@@ -11940,7 +11969,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>40</v>
       </c>
@@ -11993,7 +12022,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>41</v>
       </c>
@@ -12046,7 +12075,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>42</v>
       </c>
@@ -12099,7 +12128,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>51</v>
       </c>
@@ -12152,7 +12181,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>52</v>
       </c>
@@ -12205,7 +12234,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>53</v>
       </c>
@@ -12258,7 +12287,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>54</v>
       </c>
@@ -12311,7 +12340,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>55</v>
       </c>
@@ -12364,7 +12393,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>56</v>
       </c>
@@ -12417,7 +12446,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>57</v>
       </c>
@@ -12470,7 +12499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>58</v>
       </c>
@@ -12523,7 +12552,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>59</v>
       </c>
@@ -12576,7 +12605,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>60</v>
       </c>
@@ -12608,7 +12637,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>65</v>
       </c>
@@ -12661,7 +12690,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>66</v>
       </c>
@@ -12714,7 +12743,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>68</v>
       </c>
@@ -12767,7 +12796,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>70</v>
       </c>
@@ -12820,7 +12849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>80</v>
       </c>
@@ -12873,7 +12902,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>89</v>
       </c>
@@ -12926,7 +12955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>90</v>
       </c>
@@ -12979,7 +13008,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>91</v>
       </c>
@@ -13032,7 +13061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>92</v>
       </c>
@@ -13085,7 +13114,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>93</v>
       </c>
@@ -13138,7 +13167,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>94</v>
       </c>
@@ -13191,7 +13220,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>95</v>
       </c>
@@ -13244,7 +13273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>96</v>
       </c>
@@ -13297,7 +13326,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>100</v>
       </c>
@@ -13350,7 +13379,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>101</v>
       </c>
@@ -13403,7 +13432,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>110</v>
       </c>
@@ -13456,7 +13485,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>115</v>
       </c>
@@ -13509,7 +13538,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>120</v>
       </c>
@@ -13562,7 +13591,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>130</v>
       </c>
@@ -13615,7 +13644,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>135</v>
       </c>
@@ -13668,7 +13697,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>136</v>
       </c>
@@ -13721,7 +13750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>140</v>
       </c>
@@ -13774,7 +13803,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>145</v>
       </c>
@@ -13827,7 +13856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>150</v>
       </c>
@@ -13880,7 +13909,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>155</v>
       </c>
@@ -13933,7 +13962,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>160</v>
       </c>
@@ -13986,7 +14015,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>165</v>
       </c>
@@ -14039,7 +14068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>200</v>
       </c>
@@ -14095,7 +14124,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>205</v>
       </c>
@@ -14151,7 +14180,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>210</v>
       </c>
@@ -14204,7 +14233,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>211</v>
       </c>
@@ -14257,7 +14286,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>212</v>
       </c>
@@ -14310,7 +14339,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>220</v>
       </c>
@@ -14363,7 +14392,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>221</v>
       </c>
@@ -14416,7 +14445,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>223</v>
       </c>
@@ -14469,7 +14498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>225</v>
       </c>
@@ -14522,7 +14551,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>230</v>
       </c>
@@ -14575,7 +14604,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>231</v>
       </c>
@@ -14628,7 +14657,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>232</v>
       </c>
@@ -14681,7 +14710,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>235</v>
       </c>
@@ -14734,7 +14763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>239</v>
       </c>
@@ -14787,7 +14816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>240</v>
       </c>
@@ -14840,7 +14869,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>241</v>
       </c>
@@ -14893,7 +14922,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>242</v>
       </c>
@@ -14946,7 +14975,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>243</v>
       </c>
@@ -14999,7 +15028,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>244</v>
       </c>
@@ -15052,7 +15081,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>245</v>
       </c>
@@ -15105,7 +15134,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>246</v>
       </c>
@@ -15158,7 +15187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>247</v>
       </c>
@@ -15211,7 +15240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>248</v>
       </c>
@@ -15264,7 +15293,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>250</v>
       </c>
@@ -15317,7 +15346,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>251</v>
       </c>
@@ -15370,7 +15399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>252</v>
       </c>
@@ -15423,7 +15452,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>253</v>
       </c>
@@ -15476,7 +15505,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>254</v>
       </c>
@@ -15529,7 +15558,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>255</v>
       </c>
@@ -15582,7 +15611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>256</v>
       </c>
@@ -15635,7 +15664,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>257</v>
       </c>
@@ -15688,7 +15717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>258</v>
       </c>
@@ -15741,7 +15770,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>259</v>
       </c>
@@ -15794,7 +15823,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>261</v>
       </c>
@@ -15847,7 +15876,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>262</v>
       </c>
@@ -15900,7 +15929,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>264</v>
       </c>
@@ -15953,7 +15982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>265</v>
       </c>
@@ -15979,7 +16008,7 @@
         <v>3557</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>266</v>
       </c>
@@ -16032,7 +16061,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>267</v>
       </c>
@@ -16085,7 +16114,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>268</v>
       </c>
@@ -16138,7 +16167,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>269</v>
       </c>
@@ -16191,7 +16220,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>270</v>
       </c>
@@ -16244,7 +16273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>271</v>
       </c>
@@ -16297,7 +16326,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="97" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>272</v>
       </c>
@@ -16350,7 +16379,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="98" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>273</v>
       </c>
@@ -16403,7 +16432,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>274</v>
       </c>
@@ -16456,7 +16485,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>275</v>
       </c>
@@ -16509,7 +16538,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="101" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>276</v>
       </c>
@@ -16562,7 +16591,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>277</v>
       </c>
@@ -16615,7 +16644,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>280</v>
       </c>
@@ -16668,7 +16697,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>290</v>
       </c>
@@ -16724,7 +16753,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>291</v>
       </c>
@@ -16780,7 +16809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="106" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>300</v>
       </c>
@@ -16833,7 +16862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>305</v>
       </c>
@@ -16886,7 +16915,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>310</v>
       </c>
@@ -16942,7 +16971,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>315</v>
       </c>
@@ -16998,7 +17027,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>316</v>
       </c>
@@ -17024,7 +17053,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>317</v>
       </c>
@@ -17050,7 +17079,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>324</v>
       </c>
@@ -17103,7 +17132,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>325</v>
       </c>
@@ -17156,7 +17185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>327</v>
       </c>
@@ -17209,7 +17238,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>328</v>
       </c>
@@ -17262,7 +17291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>329</v>
       </c>
@@ -17315,7 +17344,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>331</v>
       </c>
@@ -17368,7 +17397,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>332</v>
       </c>
@@ -17421,7 +17450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>335</v>
       </c>
@@ -17474,7 +17503,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>337</v>
       </c>
@@ -17527,7 +17556,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="121" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>338</v>
       </c>
@@ -17580,7 +17609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>339</v>
       </c>
@@ -17636,7 +17665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>341</v>
       </c>
@@ -17689,7 +17718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>342</v>
       </c>
@@ -17742,7 +17771,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>343</v>
       </c>
@@ -17771,7 +17800,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="126" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>344</v>
       </c>
@@ -17812,7 +17841,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="127" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>345</v>
       </c>
@@ -17865,7 +17894,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="128" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>346</v>
       </c>
@@ -17918,7 +17947,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>347</v>
       </c>
@@ -17947,7 +17976,7 @@
         <v>3561</v>
       </c>
     </row>
-    <row r="130" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>348</v>
       </c>
@@ -17964,7 +17993,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="131" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>349</v>
       </c>
@@ -17987,7 +18016,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="132" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>350</v>
       </c>
@@ -18040,7 +18069,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="133" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>351</v>
       </c>
@@ -18093,7 +18122,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>352</v>
       </c>
@@ -18146,7 +18175,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>355</v>
       </c>
@@ -18202,7 +18231,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="136" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>359</v>
       </c>
@@ -18231,7 +18260,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="137" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>360</v>
       </c>
@@ -18287,7 +18316,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="138" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>365</v>
       </c>
@@ -18343,7 +18372,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="139" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>366</v>
       </c>
@@ -18399,7 +18428,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>367</v>
       </c>
@@ -18455,7 +18484,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>368</v>
       </c>
@@ -18511,7 +18540,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>369</v>
       </c>
@@ -18567,7 +18596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="143" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>370</v>
       </c>
@@ -18596,7 +18625,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="144" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>371</v>
       </c>
@@ -18652,7 +18681,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>372</v>
       </c>
@@ -18708,7 +18737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>373</v>
       </c>
@@ -18734,7 +18763,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>375</v>
       </c>
@@ -18787,7 +18816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>380</v>
       </c>
@@ -18840,7 +18869,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>385</v>
       </c>
@@ -18893,7 +18922,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>390</v>
       </c>
@@ -18946,7 +18975,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>395</v>
       </c>
@@ -18999,7 +19028,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>401</v>
       </c>
@@ -19052,7 +19081,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>402</v>
       </c>
@@ -19105,7 +19134,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>403</v>
       </c>
@@ -19158,7 +19187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>404</v>
       </c>
@@ -19211,7 +19240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>411</v>
       </c>
@@ -19264,7 +19293,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>413</v>
       </c>
@@ -19317,7 +19346,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="158" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>420</v>
       </c>
@@ -19370,7 +19399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="159" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>430</v>
       </c>
@@ -19423,7 +19452,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>432</v>
       </c>
@@ -19476,7 +19505,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>433</v>
       </c>
@@ -19529,7 +19558,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>434</v>
       </c>
@@ -19582,7 +19611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>435</v>
       </c>
@@ -19611,7 +19640,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>436</v>
       </c>
@@ -19664,7 +19693,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>437</v>
       </c>
@@ -19717,7 +19746,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>438</v>
       </c>
@@ -19770,7 +19799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>439</v>
       </c>
@@ -19814,7 +19843,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>450</v>
       </c>
@@ -19867,7 +19896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>451</v>
       </c>
@@ -19920,7 +19949,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>452</v>
       </c>
@@ -19973,7 +20002,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>460</v>
       </c>
@@ -20026,7 +20055,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>461</v>
       </c>
@@ -20079,7 +20108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>462</v>
       </c>
@@ -20132,7 +20161,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>470</v>
       </c>
@@ -20185,7 +20214,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>471</v>
       </c>
@@ -20238,7 +20267,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>472</v>
       </c>
@@ -20291,7 +20320,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>475</v>
       </c>
@@ -20344,7 +20373,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>480</v>
       </c>
@@ -20397,7 +20426,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>481</v>
       </c>
@@ -20450,7 +20479,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>482</v>
       </c>
@@ -20482,7 +20511,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>483</v>
       </c>
@@ -20535,7 +20564,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>484</v>
       </c>
@@ -20588,7 +20617,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>490</v>
       </c>
@@ -20641,7 +20670,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>500</v>
       </c>
@@ -20694,7 +20723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>501</v>
       </c>
@@ -20747,7 +20776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>510</v>
       </c>
@@ -20800,7 +20829,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>511</v>
       </c>
@@ -20853,7 +20882,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>512</v>
       </c>
@@ -20906,7 +20935,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>515</v>
       </c>
@@ -20959,7 +20988,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>516</v>
       </c>
@@ -21012,7 +21041,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>517</v>
       </c>
@@ -21065,7 +21094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>520</v>
       </c>
@@ -21118,7 +21147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>521</v>
       </c>
@@ -21171,7 +21200,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>522</v>
       </c>
@@ -21224,7 +21253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>530</v>
       </c>
@@ -21277,7 +21306,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>531</v>
       </c>
@@ -21330,7 +21359,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>540</v>
       </c>
@@ -21383,7 +21412,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>541</v>
       </c>
@@ -21436,7 +21465,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>551</v>
       </c>
@@ -21489,7 +21518,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>552</v>
       </c>
@@ -21542,7 +21571,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>553</v>
       </c>
@@ -21595,7 +21624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>560</v>
       </c>
@@ -21648,7 +21677,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>561</v>
       </c>
@@ -21701,7 +21730,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>562</v>
       </c>
@@ -21754,7 +21783,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>563</v>
       </c>
@@ -21807,7 +21836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>564</v>
       </c>
@@ -21860,7 +21889,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>565</v>
       </c>
@@ -21913,7 +21942,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>570</v>
       </c>
@@ -21966,7 +21995,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>571</v>
       </c>
@@ -22019,7 +22048,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>572</v>
       </c>
@@ -22072,7 +22101,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>580</v>
       </c>
@@ -22125,7 +22154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>581</v>
       </c>
@@ -22178,7 +22207,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>585</v>
       </c>
@@ -22231,7 +22260,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>590</v>
       </c>
@@ -22284,7 +22313,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>591</v>
       </c>
@@ -22337,7 +22366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>600</v>
       </c>
@@ -22390,7 +22419,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>601</v>
       </c>
@@ -22443,7 +22472,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>602</v>
       </c>
@@ -22496,7 +22525,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>615</v>
       </c>
@@ -22549,7 +22578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>616</v>
       </c>
@@ -22602,7 +22631,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>620</v>
       </c>
@@ -22655,7 +22684,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>625</v>
       </c>
@@ -22708,7 +22737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>626</v>
       </c>
@@ -22725,7 +22754,7 @@
         <v>3503</v>
       </c>
     </row>
-    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>630</v>
       </c>
@@ -22778,7 +22807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>640</v>
       </c>
@@ -22831,7 +22860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>645</v>
       </c>
@@ -22940,7 +22969,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>652</v>
       </c>
@@ -22996,7 +23025,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>660</v>
       </c>
@@ -23028,7 +23057,7 @@
         <v>3523</v>
       </c>
     </row>
-    <row r="230" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>663</v>
       </c>
@@ -23057,7 +23086,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>665</v>
       </c>
@@ -23113,7 +23142,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>666</v>
       </c>
@@ -23130,7 +23159,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>670</v>
       </c>
@@ -23183,7 +23212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>672</v>
       </c>
@@ -23236,7 +23265,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>674</v>
       </c>
@@ -23289,7 +23318,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>678</v>
       </c>
@@ -23345,7 +23374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>679</v>
       </c>
@@ -23362,7 +23391,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>680</v>
       </c>
@@ -23382,7 +23411,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>681</v>
       </c>
@@ -23435,7 +23464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>690</v>
       </c>
@@ -23488,7 +23517,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="241" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>692</v>
       </c>
@@ -23541,7 +23570,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="242" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>694</v>
       </c>
@@ -23594,7 +23623,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="243" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>696</v>
       </c>
@@ -23647,7 +23676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="244" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>698</v>
       </c>
@@ -23700,7 +23729,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="245" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>700</v>
       </c>
@@ -23756,7 +23785,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="246" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>701</v>
       </c>
@@ -23782,7 +23811,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="247" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>702</v>
       </c>
@@ -23808,7 +23837,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="248" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>703</v>
       </c>
@@ -23831,7 +23860,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="249" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>704</v>
       </c>
@@ -23860,7 +23889,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="250" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>705</v>
       </c>
@@ -23883,7 +23912,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="251" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>710</v>
       </c>
@@ -23939,7 +23968,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="252" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>711</v>
       </c>
@@ -23995,7 +24024,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="253" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>712</v>
       </c>
@@ -24051,7 +24080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="254" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>713</v>
       </c>
@@ -24107,7 +24136,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="255" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>720</v>
       </c>
@@ -24163,7 +24192,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="256" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>721</v>
       </c>
@@ -24219,7 +24248,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="257" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>730</v>
       </c>
@@ -24275,7 +24304,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="258" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>731</v>
       </c>
@@ -24298,7 +24327,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="259" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>732</v>
       </c>
@@ -24321,7 +24350,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="260" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>735</v>
       </c>
@@ -24374,7 +24403,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="261" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>740</v>
       </c>
@@ -24430,7 +24459,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="262" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>741</v>
       </c>
@@ -24486,7 +24515,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="263" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>750</v>
       </c>
@@ -24542,7 +24571,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="264" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>751</v>
       </c>
@@ -24598,7 +24627,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="265" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>752</v>
       </c>
@@ -24654,7 +24683,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="266" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>760</v>
       </c>
@@ -24710,7 +24739,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="267" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>761</v>
       </c>
@@ -24766,7 +24795,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="268" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>770</v>
       </c>
@@ -24789,7 +24818,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="269" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>771</v>
       </c>
@@ -24812,7 +24841,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="270" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>775</v>
       </c>
@@ -24868,7 +24897,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="271" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>780</v>
       </c>
@@ -24924,7 +24953,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="272" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>781</v>
       </c>
@@ -24980,7 +25009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="273" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>790</v>
       </c>
@@ -25036,7 +25065,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="274" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>800</v>
       </c>
@@ -25092,7 +25121,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="275" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>810</v>
       </c>
@@ -25148,7 +25177,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="276" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>811</v>
       </c>
@@ -25204,7 +25233,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="277" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>812</v>
       </c>
@@ -25239,7 +25268,7 @@
         <v>3522</v>
       </c>
     </row>
-    <row r="278" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>815</v>
       </c>
@@ -25295,7 +25324,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="279" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>820</v>
       </c>
@@ -25324,7 +25353,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="280" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>821</v>
       </c>
@@ -25380,7 +25409,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="281" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>823</v>
       </c>
@@ -25436,7 +25465,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="282" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>824</v>
       </c>
@@ -25492,7 +25521,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="283" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>827</v>
       </c>
@@ -25548,7 +25577,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="284" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>830</v>
       </c>
@@ -25583,7 +25612,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="285" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>835</v>
       </c>
@@ -25639,7 +25668,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="286" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>840</v>
       </c>
@@ -25695,7 +25724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="287" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>850</v>
       </c>
@@ -25751,7 +25780,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="288" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>860</v>
       </c>
@@ -25807,7 +25836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="289" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>900</v>
       </c>
@@ -25863,7 +25892,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="290" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>901</v>
       </c>
@@ -25919,7 +25948,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="291" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>902</v>
       </c>
@@ -25975,7 +26004,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="292" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>903</v>
       </c>
@@ -26031,7 +26060,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="293" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>904</v>
       </c>
@@ -26087,7 +26116,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="294" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>905</v>
       </c>
@@ -26143,7 +26172,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="295" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>906</v>
       </c>
@@ -26199,7 +26228,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="296" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>910</v>
       </c>
@@ -26225,7 +26254,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="297" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>911</v>
       </c>
@@ -26281,7 +26310,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="298" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>912</v>
       </c>
@@ -26337,7 +26366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="299" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>920</v>
       </c>
@@ -26393,7 +26422,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="300" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>925</v>
       </c>
@@ -26449,7 +26478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="301" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>930</v>
       </c>
@@ -26505,7 +26534,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="302" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>935</v>
       </c>
@@ -26561,7 +26590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="303" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>940</v>
       </c>
@@ -26617,7 +26646,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="304" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>945</v>
       </c>
@@ -26673,7 +26702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="305" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>946</v>
       </c>
@@ -26702,7 +26731,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="306" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>947</v>
       </c>
@@ -26731,7 +26760,7 @@
         <v>3580</v>
       </c>
     </row>
-    <row r="307" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>950</v>
       </c>
@@ -26787,7 +26816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="308" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>955</v>
       </c>
@@ -26843,7 +26872,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="309" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>960</v>
       </c>
@@ -26899,7 +26928,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="310" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>970</v>
       </c>
@@ -26955,7 +26984,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="311" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>980</v>
       </c>
@@ -27011,7 +27040,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="312" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>983</v>
       </c>
@@ -27067,7 +27096,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="313" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>985</v>
       </c>
@@ -27123,7 +27152,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="314" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>986</v>
       </c>
@@ -27149,7 +27178,7 @@
         <v>3576</v>
       </c>
     </row>
-    <row r="315" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>987</v>
       </c>
@@ -27178,7 +27207,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="316" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>990</v>
       </c>
@@ -27234,7 +27263,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="317" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>991</v>
       </c>
@@ -27290,7 +27319,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="318" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>1001</v>
       </c>
@@ -27343,7 +27372,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="319" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>1002</v>
       </c>
@@ -27396,7 +27425,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="320" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>1016</v>
       </c>
@@ -27449,7 +27478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>1019</v>
       </c>
@@ -27505,7 +27534,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1020</v>
       </c>
@@ -27558,7 +27587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>1022</v>
       </c>
@@ -27611,7 +27640,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>1023</v>
       </c>
@@ -27664,7 +27693,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>1024</v>
       </c>
@@ -27717,7 +27746,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>1025</v>
       </c>
@@ -27770,7 +27799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>1026</v>
       </c>
@@ -27823,7 +27852,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>1027</v>
       </c>
@@ -27876,7 +27905,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>1028</v>
       </c>
@@ -27929,7 +27958,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>1029</v>
       </c>
@@ -27982,7 +28011,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="331" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>1032</v>
       </c>
@@ -28035,7 +28064,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>1033</v>
       </c>
@@ -28088,7 +28117,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>1044</v>
       </c>
@@ -28141,7 +28170,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>1048</v>
       </c>
@@ -28194,7 +28223,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>1049</v>
       </c>
@@ -28247,7 +28276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>1053</v>
       </c>
@@ -28300,7 +28329,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>1054</v>
       </c>
@@ -28353,7 +28382,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>1055</v>
       </c>
@@ -28406,7 +28435,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>1058</v>
       </c>
@@ -28459,7 +28488,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="340" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>1061</v>
       </c>
@@ -28512,7 +28541,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>1062</v>
       </c>
@@ -28565,7 +28594,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>1063</v>
       </c>
@@ -28618,7 +28647,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>1064</v>
       </c>
@@ -28671,7 +28700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="344" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>1065</v>
       </c>
@@ -28697,7 +28726,7 @@
         <v>3507</v>
       </c>
     </row>
-    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>1069</v>
       </c>
@@ -28720,7 +28749,7 @@
         <v>3505</v>
       </c>
     </row>
-    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>1072</v>
       </c>
@@ -28773,7 +28802,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>1073</v>
       </c>
@@ -28796,7 +28825,7 @@
         <v>3507</v>
       </c>
     </row>
-    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>1075</v>
       </c>
@@ -28849,7 +28878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>1076</v>
       </c>
@@ -28902,7 +28931,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>1081</v>
       </c>
@@ -28955,7 +28984,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>1087</v>
       </c>
@@ -29011,7 +29040,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>1094</v>
       </c>
@@ -29064,7 +29093,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>1102</v>
       </c>
@@ -29120,7 +29149,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="354" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1103</v>
       </c>
@@ -29176,7 +29205,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>1105</v>
       </c>
@@ -29229,7 +29258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>1106</v>
       </c>
@@ -29282,7 +29311,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>1111</v>
       </c>
@@ -29338,7 +29367,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>1156</v>
       </c>
@@ -29391,7 +29420,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>1161</v>
       </c>
@@ -29444,7 +29473,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>1163</v>
       </c>
@@ -29497,7 +29526,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>1164</v>
       </c>
@@ -29550,7 +29579,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>2003</v>
       </c>
@@ -29606,7 +29635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>2004</v>
       </c>
@@ -29662,7 +29691,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>2101</v>
       </c>
@@ -29715,7 +29744,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>2111</v>
       </c>
@@ -29768,7 +29797,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>2246</v>
       </c>
@@ -29821,7 +29850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>2247</v>
       </c>
@@ -29874,7 +29903,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>2248</v>
       </c>
@@ -29927,7 +29956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>2249</v>
       </c>
@@ -29980,7 +30009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>2311</v>
       </c>
@@ -30033,7 +30062,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>2333</v>
       </c>
@@ -30086,7 +30115,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>2556</v>
       </c>
@@ -30139,7 +30168,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>2901</v>
       </c>
@@ -30192,7 +30221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>2902</v>
       </c>
@@ -30248,7 +30277,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>2903</v>
       </c>
@@ -30304,7 +30333,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>3271</v>
       </c>
@@ -30357,7 +30386,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>3327</v>
       </c>
@@ -30410,7 +30439,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>3340</v>
       </c>
@@ -30463,7 +30492,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>3343</v>
       </c>
@@ -30516,7 +30545,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>3349</v>
       </c>
@@ -30569,7 +30598,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>3353</v>
       </c>
@@ -30622,7 +30651,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>3361</v>
       </c>
@@ -30678,7 +30707,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>3362</v>
       </c>
@@ -30734,7 +30763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>3363</v>
       </c>
@@ -30790,7 +30819,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>3386</v>
       </c>
@@ -30843,7 +30872,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>3471</v>
       </c>
@@ -30896,7 +30925,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>3502</v>
       </c>
@@ -30949,7 +30978,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>3503</v>
       </c>
@@ -31002,7 +31031,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>3504</v>
       </c>
@@ -31055,7 +31084,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>3551</v>
       </c>
@@ -31111,7 +31140,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>3654</v>
       </c>
@@ -31164,7 +31193,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>3761</v>
       </c>
@@ -31217,7 +31246,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>3762</v>
       </c>
@@ -31270,7 +31299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>3805</v>
       </c>
@@ -31323,7 +31352,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>4041</v>
       </c>
@@ -31376,7 +31405,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>4042</v>
       </c>
@@ -31429,7 +31458,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>4044</v>
       </c>
@@ -31482,7 +31511,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>4050</v>
       </c>
@@ -31535,7 +31564,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>4060</v>
       </c>
@@ -31588,7 +31617,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>4070</v>
       </c>
@@ -31641,7 +31670,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>4111</v>
       </c>
@@ -31694,7 +31723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>4112</v>
       </c>
@@ -31747,7 +31776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>4325</v>
       </c>
@@ -31800,7 +31829,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>4326</v>
       </c>
@@ -31853,7 +31882,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>4327</v>
       </c>
@@ -31906,7 +31935,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>4328</v>
       </c>
@@ -31959,7 +31988,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>4331</v>
       </c>
@@ -32012,7 +32041,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>4332</v>
       </c>
@@ -32065,7 +32094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>4333</v>
       </c>
@@ -32118,7 +32147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>4334</v>
       </c>
@@ -32171,7 +32200,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>4335</v>
       </c>
@@ -32224,7 +32253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>4336</v>
       </c>
@@ -32277,7 +32306,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>4337</v>
       </c>
@@ -32330,7 +32359,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>4338</v>
       </c>
@@ -32383,7 +32412,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>4341</v>
       </c>
@@ -32436,7 +32465,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>4343</v>
       </c>
@@ -32489,7 +32518,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>4345</v>
       </c>
@@ -32542,7 +32571,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>4347</v>
       </c>
@@ -32595,7 +32624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>4348</v>
       </c>
@@ -32648,7 +32677,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>4349</v>
       </c>
@@ -32701,7 +32730,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>4352</v>
       </c>
@@ -32754,7 +32783,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>4354</v>
       </c>
@@ -32807,7 +32836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>4361</v>
       </c>
@@ -32860,7 +32889,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>4362</v>
       </c>
@@ -32913,7 +32942,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>4381</v>
       </c>
@@ -32966,7 +32995,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>4382</v>
       </c>
@@ -33019,7 +33048,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>4383</v>
       </c>
@@ -33072,7 +33101,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>4391</v>
       </c>
@@ -33125,7 +33154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>4392</v>
       </c>
@@ -33178,7 +33207,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>4394</v>
       </c>
@@ -33231,7 +33260,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>4395</v>
       </c>
@@ -33284,7 +33313,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>4396</v>
       </c>
@@ -33337,7 +33366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>4397</v>
       </c>
@@ -33390,7 +33419,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="434" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>4501</v>
       </c>
@@ -33443,7 +33472,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="435" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>4515</v>
       </c>
@@ -33496,7 +33525,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="436" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>4521</v>
       </c>
@@ -33549,7 +33578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="437" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>4527</v>
       </c>
@@ -33602,7 +33631,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="438" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>4529</v>
       </c>
@@ -33655,7 +33684,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="439" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>4534</v>
       </c>
@@ -33708,7 +33737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="440" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>4535</v>
       </c>
@@ -33761,7 +33790,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="441" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>4711</v>
       </c>
@@ -33814,7 +33843,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="442" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>4737</v>
       </c>
@@ -33867,7 +33896,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="443" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>4741</v>
       </c>
@@ -33920,7 +33949,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="444" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>4742</v>
       </c>
@@ -33973,7 +34002,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="445" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>4744</v>
       </c>
@@ -34026,7 +34055,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="446" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>4746</v>
       </c>
@@ -34079,7 +34108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="447" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>4751</v>
       </c>
@@ -34132,7 +34161,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="448" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>4763</v>
       </c>
@@ -34185,7 +34214,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="449" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>4769</v>
       </c>
@@ -34238,7 +34267,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="450" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>4773</v>
       </c>
@@ -34291,7 +34320,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="451" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>4776</v>
       </c>
@@ -34344,7 +34373,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="452" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>4781</v>
       </c>
@@ -34397,7 +34426,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="453" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>4782</v>
       </c>
@@ -34450,7 +34479,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="454" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>4783</v>
       </c>
@@ -34503,7 +34532,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="455" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>4784</v>
       </c>
@@ -34556,7 +34585,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="456" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>4791</v>
       </c>
@@ -34609,7 +34638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="457" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>4792</v>
       </c>
@@ -34662,7 +34691,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="458" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>4793</v>
       </c>
@@ -34715,7 +34744,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="459" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>4795</v>
       </c>
@@ -34768,7 +34797,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="460" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>4821</v>
       </c>
@@ -34821,7 +34850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="461" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>4822</v>
       </c>
@@ -34874,7 +34903,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="462" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>4831</v>
       </c>
@@ -34927,7 +34956,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="463" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>4832</v>
       </c>
@@ -34980,7 +35009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="464" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>4841</v>
       </c>
@@ -35033,7 +35062,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="465" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>4842</v>
       </c>
@@ -35086,7 +35115,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="466" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>4902</v>
       </c>
@@ -35139,7 +35168,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="467" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>4904</v>
       </c>
@@ -35192,7 +35221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="468" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>4908</v>
       </c>
@@ -35245,7 +35274,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="469" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A469">
         <v>4910</v>
       </c>
@@ -35298,7 +35327,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="470" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>5001</v>
       </c>
@@ -35351,7 +35380,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="471" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>5002</v>
       </c>
@@ -35404,7 +35433,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="472" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>5003</v>
       </c>
@@ -35457,7 +35486,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="473" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>5011</v>
       </c>
@@ -35510,7 +35539,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="474" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A474">
         <v>5013</v>
       </c>
@@ -35563,7 +35592,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="475" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>5018</v>
       </c>
@@ -35616,7 +35645,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="476" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>5102</v>
       </c>
@@ -35669,7 +35698,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="477" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>5104</v>
       </c>
@@ -35722,7 +35751,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="478" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>5109</v>
       </c>
@@ -35778,7 +35807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="479" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A479">
         <v>5200</v>
       </c>
@@ -35831,7 +35860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="480" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>5201</v>
       </c>
@@ -35884,7 +35913,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>5203</v>
       </c>
@@ -35937,7 +35966,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>5212</v>
       </c>
@@ -35990,7 +36019,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>5303</v>
       </c>
@@ -36043,7 +36072,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>5306</v>
       </c>
@@ -36096,7 +36125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>5307</v>
       </c>
@@ -36149,7 +36178,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>5309</v>
       </c>
@@ -36202,7 +36231,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>5321</v>
       </c>
@@ -36255,7 +36284,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>5322</v>
       </c>
@@ -36308,7 +36337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>5323</v>
       </c>
@@ -36361,7 +36390,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="490" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>5324</v>
       </c>
@@ -36414,7 +36443,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="491" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>5332</v>
       </c>
@@ -36467,7 +36496,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>5403</v>
       </c>
@@ -36520,7 +36549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>5511</v>
       </c>
@@ -36573,7 +36602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>5512</v>
       </c>
@@ -36626,7 +36655,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>5513</v>
       </c>
@@ -36679,7 +36708,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="496" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>5516</v>
       </c>
@@ -36732,7 +36761,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="497" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>5517</v>
       </c>
@@ -36785,7 +36814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="498" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>5518</v>
       </c>
@@ -36838,7 +36867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="499" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>5519</v>
       </c>
@@ -36891,7 +36920,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="500" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>5522</v>
       </c>
@@ -36944,7 +36973,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="501" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>5523</v>
       </c>
@@ -36997,7 +37026,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="502" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>5606</v>
       </c>
@@ -37050,7 +37079,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="503" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>5611</v>
       </c>
@@ -37103,7 +37132,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="504" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>5614</v>
       </c>
@@ -37156,7 +37185,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="505" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>5621</v>
       </c>
@@ -37209,7 +37238,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="506" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>5641</v>
       </c>
@@ -37262,7 +37291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="507" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A507">
         <v>5642</v>
       </c>
@@ -37315,7 +37344,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="508" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A508">
         <v>5651</v>
       </c>
@@ -37368,7 +37397,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="509" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>5796</v>
       </c>
@@ -37421,7 +37450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="510" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>5799</v>
       </c>
@@ -37474,7 +37503,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="511" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>5801</v>
       </c>
@@ -37527,7 +37556,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="512" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A512">
         <v>5802</v>
       </c>
@@ -37580,7 +37609,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="513" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>5803</v>
       </c>
@@ -37633,7 +37662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="514" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>5811</v>
       </c>
@@ -37686,7 +37715,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="515" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>5812</v>
       </c>
@@ -37739,7 +37768,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="516" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A516">
         <v>5813</v>
       </c>
@@ -37792,7 +37821,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="517" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A517">
         <v>5814</v>
       </c>
@@ -37845,7 +37874,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="518" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A518">
         <v>5901</v>
       </c>
@@ -37898,7 +37927,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="519" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A519">
         <v>5902</v>
       </c>
@@ -37951,7 +37980,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="520" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A520">
         <v>5903</v>
       </c>
@@ -38004,7 +38033,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="521" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A521">
         <v>6030</v>
       </c>
@@ -38057,7 +38086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="522" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A522">
         <v>6062</v>
       </c>
@@ -38113,7 +38142,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="523" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A523">
         <v>6064</v>
       </c>
@@ -38169,7 +38198,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="524" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A524">
         <v>6067</v>
       </c>
@@ -38222,7 +38251,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="525" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A525">
         <v>6090</v>
       </c>
@@ -38275,7 +38304,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="526" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A526">
         <v>6151</v>
       </c>
@@ -38328,7 +38357,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="527" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A527">
         <v>6202</v>
       </c>
@@ -38384,7 +38413,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="528" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A528">
         <v>6203</v>
       </c>
@@ -38440,7 +38469,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="529" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A529">
         <v>6251</v>
       </c>
@@ -38493,7 +38522,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="530" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A530">
         <v>6255</v>
       </c>
@@ -38549,7 +38578,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A531">
         <v>6306</v>
       </c>
@@ -38602,7 +38631,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A532">
         <v>6401</v>
       </c>
@@ -38655,7 +38684,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A533">
         <v>6402</v>
       </c>
@@ -38708,7 +38737,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A534">
         <v>6631</v>
       </c>
@@ -38734,7 +38763,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A535">
         <v>6800</v>
       </c>
@@ -38787,7 +38816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="536" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A536">
         <v>6802</v>
       </c>
@@ -38840,7 +38869,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A537">
         <v>6811</v>
       </c>
@@ -38893,7 +38922,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A538">
         <v>6821</v>
       </c>
@@ -38946,7 +38975,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="539" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A539">
         <v>6822</v>
       </c>
@@ -38999,7 +39028,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="540" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A540">
         <v>6823</v>
       </c>
@@ -39052,7 +39081,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="541" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A541">
         <v>6825</v>
       </c>
@@ -39105,7 +39134,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A542">
         <v>6826</v>
       </c>
@@ -39158,7 +39187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A543">
         <v>6828</v>
       </c>
@@ -39211,7 +39240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="544" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A544">
         <v>6832</v>
       </c>
@@ -39264,7 +39293,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="545" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A545">
         <v>6833</v>
       </c>
@@ -39317,7 +39346,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A546">
         <v>6844</v>
       </c>
@@ -39370,7 +39399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A547">
         <v>6845</v>
       </c>
@@ -39423,7 +39452,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="548" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A548">
         <v>6846</v>
       </c>
@@ -39476,7 +39505,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="549" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A549">
         <v>6982</v>
       </c>
@@ -39529,7 +39558,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A550">
         <v>7010</v>
       </c>
@@ -39582,7 +39611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A551">
         <v>7020</v>
       </c>
@@ -39635,7 +39664,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A552">
         <v>7030</v>
       </c>
@@ -39688,7 +39717,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A553">
         <v>7104</v>
       </c>
@@ -39744,7 +39773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A554">
         <v>7105</v>
       </c>
@@ -39800,7 +39829,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A555">
         <v>7106</v>
       </c>
@@ -39856,7 +39885,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A556">
         <v>7110</v>
       </c>
@@ -39912,7 +39941,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A557">
         <v>7111</v>
       </c>
@@ -39968,7 +39997,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A558">
         <v>7120</v>
       </c>
@@ -40024,7 +40053,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A559">
         <v>7121</v>
       </c>
@@ -40080,7 +40109,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A560">
         <v>7122</v>
       </c>
@@ -40136,7 +40165,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="561" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A561">
         <v>7124</v>
       </c>
@@ -40192,7 +40221,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="562" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A562">
         <v>7125</v>
       </c>
@@ -40248,7 +40277,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="563" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A563">
         <v>7127</v>
       </c>
@@ -40304,7 +40333,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="564" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A564">
         <v>7136</v>
       </c>
@@ -40360,7 +40389,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="565" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A565">
         <v>7137</v>
       </c>
@@ -40416,7 +40445,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="566" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A566">
         <v>7351</v>
       </c>
@@ -40470,7 +40499,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="567" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A567">
         <v>7352</v>
       </c>
@@ -40526,7 +40555,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="568" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A568">
         <v>7411</v>
       </c>
@@ -40582,7 +40611,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="569" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A569">
         <v>7501</v>
       </c>
@@ -40638,7 +40667,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="570" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A570">
         <v>7502</v>
       </c>
@@ -40694,7 +40723,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="571" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A571">
         <v>7506</v>
       </c>
@@ -40750,7 +40779,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="572" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A572">
         <v>7508</v>
       </c>
@@ -40806,7 +40835,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="573" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A573">
         <v>7511</v>
       </c>
@@ -40862,7 +40891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="574" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A574">
         <v>7512</v>
       </c>
@@ -40918,7 +40947,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="575" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A575">
         <v>7513</v>
       </c>
@@ -40974,7 +41003,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="576" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A576">
         <v>7514</v>
       </c>
@@ -41030,7 +41059,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="577" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A577">
         <v>7515</v>
       </c>
@@ -41086,7 +41115,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="578" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A578">
         <v>7516</v>
       </c>
@@ -41142,7 +41171,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="579" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A579">
         <v>7517</v>
       </c>
@@ -41198,7 +41227,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="580" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A580">
         <v>7519</v>
       </c>
@@ -41254,7 +41283,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="581" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A581">
         <v>7521</v>
       </c>
@@ -41310,7 +41339,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="582" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A582">
         <v>7522</v>
       </c>
@@ -41366,7 +41395,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="583" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A583">
         <v>7523</v>
       </c>
@@ -41422,7 +41451,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="584" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A584">
         <v>7526</v>
       </c>
@@ -41478,7 +41507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="585" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A585">
         <v>7527</v>
       </c>
@@ -41534,7 +41563,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="586" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A586">
         <v>7528</v>
       </c>
@@ -41590,7 +41619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="587" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A587">
         <v>7529</v>
       </c>
@@ -41646,7 +41675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="588" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A588">
         <v>7531</v>
       </c>
@@ -41702,7 +41731,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="589" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A589">
         <v>7532</v>
       </c>
@@ -41758,7 +41787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="590" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A590">
         <v>7533</v>
       </c>
@@ -41814,7 +41843,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="591" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A591">
         <v>7534</v>
       </c>
@@ -41870,7 +41899,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="592" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A592">
         <v>7535</v>
       </c>
@@ -41926,7 +41955,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="593" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A593">
         <v>7537</v>
       </c>
@@ -41982,7 +42011,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="594" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A594">
         <v>7538</v>
       </c>
@@ -42038,7 +42067,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="595" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A595">
         <v>7539</v>
       </c>
@@ -42094,7 +42123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="596" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A596">
         <v>7541</v>
       </c>
@@ -42150,7 +42179,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="597" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A597">
         <v>7542</v>
       </c>
@@ -42206,7 +42235,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="598" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A598">
         <v>7543</v>
       </c>
@@ -42262,7 +42291,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="599" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A599">
         <v>7544</v>
       </c>
@@ -42318,7 +42347,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="600" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A600">
         <v>7545</v>
       </c>
@@ -42374,7 +42403,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="601" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A601">
         <v>7546</v>
       </c>
@@ -42430,7 +42459,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="602" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A602">
         <v>7549</v>
       </c>
@@ -42486,7 +42515,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="603" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A603">
         <v>7552</v>
       </c>
@@ -42542,7 +42571,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="604" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A604">
         <v>7553</v>
       </c>
@@ -42598,7 +42627,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="605" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A605">
         <v>7570</v>
       </c>
@@ -42654,7 +42683,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="606" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A606">
         <v>7573</v>
       </c>
@@ -42710,7 +42739,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="607" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A607">
         <v>7574</v>
       </c>
@@ -42766,7 +42795,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="608" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A608">
         <v>7577</v>
       </c>
@@ -42822,7 +42851,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="609" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A609">
         <v>7579</v>
       </c>
@@ -42878,7 +42907,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="610" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A610">
         <v>7582</v>
       </c>
@@ -42934,7 +42963,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="611" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A611">
         <v>7587</v>
       </c>
@@ -42990,7 +43019,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="612" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A612">
         <v>7588</v>
       </c>
@@ -43046,7 +43075,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="613" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A613">
         <v>7694</v>
       </c>
@@ -43102,7 +43131,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="614" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A614">
         <v>7701</v>
       </c>
@@ -43158,7 +43187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="615" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A615">
         <v>7702</v>
       </c>
@@ -43214,7 +43243,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="616" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A616">
         <v>7703</v>
       </c>
@@ -43270,7 +43299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="617" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A617">
         <v>7704</v>
       </c>
@@ -43326,7 +43355,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="618" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A618">
         <v>7706</v>
       </c>
@@ -43382,7 +43411,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="619" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A619">
         <v>7707</v>
       </c>
@@ -43441,7 +43470,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="620" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A620">
         <v>7750</v>
       </c>
@@ -43497,7 +43526,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="621" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A621">
         <v>7751</v>
       </c>
@@ -43553,7 +43582,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="622" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A622">
         <v>7752</v>
       </c>
@@ -43609,7 +43638,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="623" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A623">
         <v>7755</v>
       </c>
@@ -43665,7 +43694,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="624" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A624">
         <v>7756</v>
       </c>
@@ -43721,7 +43750,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="625" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A625">
         <v>7757</v>
       </c>
@@ -43777,7 +43806,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="626" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A626">
         <v>7758</v>
       </c>
@@ -43833,7 +43862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="627" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A627">
         <v>7760</v>
       </c>
@@ -43889,7 +43918,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="628" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A628">
         <v>7762</v>
       </c>
@@ -43945,7 +43974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="629" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A629">
         <v>7766</v>
       </c>
@@ -44001,7 +44030,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="630" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A630">
         <v>7767</v>
       </c>
@@ -44057,7 +44086,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="631" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A631">
         <v>7768</v>
       </c>
@@ -44113,7 +44142,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="632" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A632">
         <v>7769</v>
       </c>
@@ -44169,7 +44198,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="633" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A633">
         <v>7770</v>
       </c>
@@ -44225,7 +44254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="634" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A634">
         <v>7771</v>
       </c>
@@ -44281,7 +44310,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="635" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A635">
         <v>7772</v>
       </c>
@@ -44337,7 +44366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="636" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A636">
         <v>7773</v>
       </c>
@@ -44393,7 +44422,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="637" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A637">
         <v>7774</v>
       </c>
@@ -44449,7 +44478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="638" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A638">
         <v>7775</v>
       </c>
@@ -44505,7 +44534,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="639" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A639">
         <v>7776</v>
       </c>
@@ -44561,7 +44590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="640" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A640">
         <v>7777</v>
       </c>
@@ -44617,7 +44646,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="641" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A641">
         <v>7778</v>
       </c>
@@ -44673,7 +44702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="642" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A642">
         <v>7779</v>
       </c>
@@ -44729,7 +44758,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="643" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A643">
         <v>7780</v>
       </c>
@@ -44785,7 +44814,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="644" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A644">
         <v>7782</v>
       </c>
@@ -44841,7 +44870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="645" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A645">
         <v>7783</v>
       </c>
@@ -44897,7 +44926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="646" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A646">
         <v>7784</v>
       </c>
@@ -44953,7 +44982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="647" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A647">
         <v>7785</v>
       </c>
@@ -45009,7 +45038,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="648" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A648">
         <v>7786</v>
       </c>
@@ -45065,7 +45094,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="649" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A649">
         <v>7787</v>
       </c>
@@ -45121,7 +45150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="650" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A650">
         <v>7788</v>
       </c>
@@ -45177,7 +45206,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="651" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A651">
         <v>7789</v>
       </c>
@@ -45233,7 +45262,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="652" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A652">
         <v>7790</v>
       </c>
@@ -45289,7 +45318,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="653" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A653">
         <v>7791</v>
       </c>
@@ -45345,7 +45374,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="654" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A654">
         <v>7792</v>
       </c>
@@ -45401,7 +45430,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="655" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A655">
         <v>7793</v>
       </c>
@@ -45457,7 +45486,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="656" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A656">
         <v>7794</v>
       </c>
@@ -45513,7 +45542,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="657" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A657">
         <v>7795</v>
       </c>
@@ -45569,7 +45598,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="658" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A658">
         <v>7796</v>
       </c>
@@ -45625,7 +45654,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="659" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A659">
         <v>7797</v>
       </c>
@@ -45681,7 +45710,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="660" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A660">
         <v>8002</v>
       </c>
@@ -45737,7 +45766,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="661" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A661">
         <v>8124</v>
       </c>
@@ -45793,7 +45822,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="662" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A662">
         <v>8151</v>
       </c>
@@ -45849,7 +45878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="663" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A663">
         <v>8152</v>
       </c>
@@ -45905,7 +45934,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="664" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A664">
         <v>8153</v>
       </c>
@@ -45961,7 +45990,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="665" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A665">
         <v>8171</v>
       </c>
@@ -46017,7 +46046,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="666" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A666">
         <v>8201</v>
       </c>
@@ -46073,7 +46102,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="667" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A667">
         <v>8202</v>
       </c>
@@ -46129,7 +46158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="668" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A668">
         <v>8203</v>
       </c>
@@ -46185,7 +46214,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="669" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A669">
         <v>8210</v>
       </c>
@@ -46241,7 +46270,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="670" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A670">
         <v>8218</v>
       </c>
@@ -46297,7 +46326,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="671" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A671">
         <v>8221</v>
       </c>
@@ -46353,7 +46382,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="672" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A672">
         <v>8222</v>
       </c>
@@ -46409,7 +46438,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="673" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A673">
         <v>8223</v>
       </c>
@@ -46465,7 +46494,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="674" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A674">
         <v>8224</v>
       </c>
@@ -46521,7 +46550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="675" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A675">
         <v>8225</v>
       </c>
@@ -46577,7 +46606,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="676" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A676">
         <v>8231</v>
       </c>
@@ -46633,7 +46662,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="677" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A677">
         <v>8401</v>
       </c>
@@ -46689,7 +46718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="678" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A678">
         <v>8501</v>
       </c>
@@ -46745,7 +46774,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="679" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A679">
         <v>8510</v>
       </c>
@@ -46801,7 +46830,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="680" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A680">
         <v>8522</v>
       </c>
@@ -46857,7 +46886,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="681" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A681">
         <v>8523</v>
       </c>
@@ -46913,7 +46942,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="682" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A682">
         <v>8531</v>
       </c>
@@ -46969,7 +46998,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="683" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A683">
         <v>8532</v>
       </c>
@@ -47025,7 +47054,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="684" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A684">
         <v>8533</v>
       </c>
@@ -47081,7 +47110,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="685" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A685">
         <v>8536</v>
       </c>
@@ -47137,7 +47166,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="686" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A686">
         <v>8550</v>
       </c>
@@ -47193,7 +47222,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="687" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A687">
         <v>8551</v>
       </c>
@@ -47249,7 +47278,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="688" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A688">
         <v>8560</v>
       </c>
@@ -47305,7 +47334,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="689" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A689">
         <v>8571</v>
       </c>
@@ -47361,7 +47390,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="690" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A690">
         <v>8572</v>
       </c>
@@ -47417,7 +47446,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="691" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A691">
         <v>8574</v>
       </c>
@@ -47473,7 +47502,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="692" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A692">
         <v>9002</v>
       </c>
@@ -47529,7 +47558,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="693" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A693">
         <v>9004</v>
       </c>
@@ -47588,7 +47617,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="694" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A694">
         <v>9006</v>
       </c>
@@ -47647,7 +47676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="695" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A695">
         <v>9008</v>
       </c>
@@ -47706,7 +47735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="696" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A696">
         <v>9050</v>
       </c>
@@ -47765,7 +47794,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="697" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A697">
         <v>9201</v>
       </c>
@@ -47821,7 +47850,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="698" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A698">
         <v>9205</v>
       </c>
@@ -47880,7 +47909,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="699" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A699">
         <v>9252</v>
       </c>
@@ -47936,7 +47965,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="700" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A700">
         <v>9253</v>
       </c>
@@ -47992,7 +48021,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="701" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A701">
         <v>9321</v>
       </c>
@@ -48048,7 +48077,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="702" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A702">
         <v>9453</v>
       </c>
@@ -48104,7 +48133,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="703" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A703">
         <v>9462</v>
       </c>
@@ -48160,7 +48189,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="704" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A704">
         <v>9601</v>
       </c>
@@ -48216,7 +48245,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="705" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A705">
         <v>9602</v>
       </c>
@@ -48272,7 +48301,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="706" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A706">
         <v>9603</v>
       </c>
@@ -48328,7 +48357,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="707" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A707">
         <v>9605</v>
       </c>
@@ -48384,7 +48413,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="708" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A708">
         <v>9610</v>
       </c>
@@ -48440,7 +48469,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="709" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A709">
         <v>9620</v>
       </c>
@@ -48496,7 +48525,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="710" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A710">
         <v>9740</v>
       </c>
@@ -48555,7 +48584,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="711" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A711">
         <v>9810</v>
       </c>
@@ -48614,7 +48643,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="712" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A712">
         <v>9820</v>
       </c>
@@ -48670,7 +48699,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="713" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A713">
         <v>9830</v>
       </c>
@@ -48726,7 +48755,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="714" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A714">
         <v>9900</v>
       </c>
@@ -48782,7 +48811,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="715" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A715">
         <v>9973</v>
       </c>
@@ -48838,7 +48867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="716" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A716">
         <v>9974</v>
       </c>
@@ -48894,7 +48923,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="717" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A717">
         <v>9994</v>
       </c>
@@ -48950,7 +48979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="718" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A718">
         <v>10200</v>
       </c>
@@ -49003,7 +49032,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="719" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A719">
         <v>10210</v>
       </c>
@@ -49056,13 +49085,163 @@
         <v>24</v>
       </c>
     </row>
+    <row r="720" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A720">
+        <v>7693</v>
+      </c>
+      <c r="B720" t="s">
+        <v>3581</v>
+      </c>
+      <c r="C720" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F720" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G720" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="721" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A721">
+        <v>3261</v>
+      </c>
+      <c r="B721" t="s">
+        <v>3582</v>
+      </c>
+      <c r="C721" t="s">
+        <v>60</v>
+      </c>
+      <c r="F721" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="722" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A722">
+        <v>9005</v>
+      </c>
+      <c r="B722" t="s">
+        <v>3583</v>
+      </c>
+      <c r="C722" t="s">
+        <v>30</v>
+      </c>
+      <c r="F722" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G722" s="2" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="723" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A723">
+        <v>4344</v>
+      </c>
+      <c r="B723" t="s">
+        <v>3584</v>
+      </c>
+      <c r="C723" t="s">
+        <v>687</v>
+      </c>
+      <c r="F723" s="1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="724" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A724">
+        <v>4114</v>
+      </c>
+      <c r="B724" t="s">
+        <v>3585</v>
+      </c>
+      <c r="C724" t="s">
+        <v>687</v>
+      </c>
+      <c r="F724" s="1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="725" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A725">
+        <v>9007</v>
+      </c>
+      <c r="B725" t="s">
+        <v>3586</v>
+      </c>
+      <c r="C725" t="s">
+        <v>30</v>
+      </c>
+      <c r="F725" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G725" s="2" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="726" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A726">
+        <v>7910</v>
+      </c>
+      <c r="B726" t="s">
+        <v>3587</v>
+      </c>
+      <c r="C726" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F726" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G726" s="1" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="727" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A727">
+        <v>5807</v>
+      </c>
+      <c r="B727" t="s">
+        <v>3588</v>
+      </c>
+      <c r="C727" t="s">
+        <v>687</v>
+      </c>
+      <c r="F727" s="1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="728" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A728">
+        <v>682</v>
+      </c>
+      <c r="B728" t="s">
+        <v>3589</v>
+      </c>
+      <c r="C728" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F728" s="1" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="729" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A729">
+        <v>984</v>
+      </c>
+      <c r="B729" t="s">
+        <v>3590</v>
+      </c>
+      <c r="C729" t="s">
+        <v>30</v>
+      </c>
+      <c r="F729" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G729" s="1" t="s">
+        <v>1168</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S719" xr:uid="{4F1F9B7D-6BBF-234F-A8E6-6117CCB385B8}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Egypt Arab Republic (Egypt)"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:S729" xr:uid="{4F1F9B7D-6BBF-234F-A8E6-6117CCB385B8}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S719">
       <sortCondition ref="A1:A719"/>
     </sortState>
